--- a/指令-通用版 20260623.xlsx
+++ b/指令-通用版 20260623.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="919">
   <si>
     <t>修改时间</t>
   </si>
@@ -1470,12 +1470,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
       <t>状态值为：</t>
     </r>
     <r>
@@ -6596,6 +6590,89 @@
   </si>
   <si>
     <t>摄像机6延时告警</t>
+  </si>
+  <si>
+    <t>0x2080 0000</t>
+  </si>
+  <si>
+    <t>主网1丢包告警</t>
+  </si>
+  <si>
+    <t>0x2090 0000</t>
+  </si>
+  <si>
+    <t>主网2丢包告警</t>
+  </si>
+  <si>
+    <t>0x20A1 0000</t>
+  </si>
+  <si>
+    <t>摄像机1丢包告警</t>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Alibaba PuHuiTi Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>位代表摄像机通道</t>
+    </r>
+  </si>
+  <si>
+    <t>0x20A2 0000</t>
+  </si>
+  <si>
+    <t>摄像机2丢包告警</t>
+  </si>
+  <si>
+    <t>0x20A3 0000</t>
+  </si>
+  <si>
+    <t>摄像机3丢包告警</t>
+  </si>
+  <si>
+    <t>0x20A4 0000</t>
+  </si>
+  <si>
+    <t>摄像机4丢包告警</t>
+  </si>
+  <si>
+    <t>0x20A5 0000</t>
+  </si>
+  <si>
+    <t>摄像机5丢包告警</t>
+  </si>
+  <si>
+    <t>0x20A6 0000</t>
+  </si>
+  <si>
+    <t>摄像机6丢包告警</t>
+  </si>
+  <si>
+    <t>0x20B0 0000</t>
+  </si>
+  <si>
+    <t>主网1 IP未配置</t>
+  </si>
+  <si>
+    <t>0x20C0 0000</t>
+  </si>
+  <si>
+    <t>主网2 IP未配置</t>
   </si>
   <si>
     <t>传感器</t>
@@ -7544,8 +7621,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Helvetica Neue"/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -7554,20 +7631,43 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="21"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="方正书宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -7589,30 +7689,7 @@
     <font>
       <sz val="10"/>
       <color indexed="21"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="方正书宋_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Helvetica Neue"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -18109,30 +18186,30 @@
   <sheetPr codeName="Sheet6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S101"/>
+  <dimension ref="B1:T101"/>
   <sheetFormatPr defaultColWidth="16.2857142857143" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="22.8571428571429" style="53" customWidth="1"/>
-    <col min="2" max="2" width="16.5238095238095" style="53" customWidth="1"/>
-    <col min="3" max="3" width="14.7809523809524" style="53" customWidth="1"/>
-    <col min="4" max="4" width="14.1428571428571" style="53" customWidth="1"/>
-    <col min="5" max="5" width="13.7142857142857" style="53" customWidth="1"/>
-    <col min="6" max="6" width="23.5714285714286" style="53" customWidth="1"/>
-    <col min="7" max="7" width="19.2857142857143" style="53" customWidth="1"/>
-    <col min="8" max="8" width="13.2857142857143" style="53" customWidth="1"/>
-    <col min="9" max="10" width="15.7142857142857" style="53" customWidth="1"/>
-    <col min="11" max="11" width="10.2857142857143" style="53" customWidth="1"/>
-    <col min="12" max="13" width="23.5714285714286" style="53" customWidth="1"/>
-    <col min="14" max="14" width="34.9047619047619" style="53" customWidth="1"/>
-    <col min="15" max="15" width="24.8571428571429" style="53" customWidth="1"/>
-    <col min="16" max="16384" width="16.2857142857143" style="53"/>
+    <col min="1" max="1" width="16.2857142857143" style="53"/>
+    <col min="2" max="2" width="22.8571428571429" style="53" customWidth="1"/>
+    <col min="3" max="3" width="16.5238095238095" style="53" customWidth="1"/>
+    <col min="4" max="4" width="14.7809523809524" style="53" customWidth="1"/>
+    <col min="5" max="5" width="14.1428571428571" style="53" customWidth="1"/>
+    <col min="6" max="6" width="13.7142857142857" style="53" customWidth="1"/>
+    <col min="7" max="7" width="23.5714285714286" style="53" customWidth="1"/>
+    <col min="8" max="8" width="19.2857142857143" style="53" customWidth="1"/>
+    <col min="9" max="9" width="13.2857142857143" style="53" customWidth="1"/>
+    <col min="10" max="11" width="15.7142857142857" style="53" customWidth="1"/>
+    <col min="12" max="12" width="10.2857142857143" style="53" customWidth="1"/>
+    <col min="13" max="14" width="23.5714285714286" style="53" customWidth="1"/>
+    <col min="15" max="15" width="34.9047619047619" style="53" customWidth="1"/>
+    <col min="16" max="16" width="24.8571428571429" style="53" customWidth="1"/>
+    <col min="17" max="16384" width="16.2857142857143" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:16">
-      <c r="A1" s="55" t="s">
+    <row r="1" ht="30" customHeight="1" spans="2:17">
+      <c r="B1" s="55" t="s">
         <v>655</v>
       </c>
-      <c r="B1" s="56"/>
       <c r="C1" s="56"/>
       <c r="D1" s="56"/>
       <c r="E1" s="56"/>
@@ -18147,137 +18224,137 @@
       <c r="N1" s="56"/>
       <c r="O1" s="56"/>
       <c r="P1" s="56"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:16">
-      <c r="A2" s="50" t="s">
+      <c r="Q1" s="56"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="2:17">
+      <c r="B2" s="50" t="s">
         <v>656</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="C2" s="50" t="s">
         <v>657</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="D2" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="E2" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="E2" s="58">
+      <c r="F2" s="58">
         <v>1</v>
       </c>
-      <c r="F2" s="44">
+      <c r="G2" s="44">
         <v>2</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="H2" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="58">
+      <c r="I2" s="58">
         <v>1</v>
-      </c>
-      <c r="I2" s="59">
-        <v>4</v>
       </c>
       <c r="J2" s="59">
         <v>4</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="59">
+        <v>4</v>
+      </c>
+      <c r="L2" s="57" t="s">
         <v>412</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="M2" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="57"/>
       <c r="N2" s="57"/>
-      <c r="O2" s="57">
+      <c r="O2" s="57"/>
+      <c r="P2" s="57">
         <v>1</v>
       </c>
-      <c r="P2" s="57">
+      <c r="Q2" s="57">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:16">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="50" t="s">
+    <row r="3" ht="24" customHeight="1" spans="2:17">
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="E3" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="G3" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="H3" s="50" t="s">
         <v>658</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="I3" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="I3" s="62" t="s">
+      <c r="J3" s="62" t="s">
         <v>659</v>
       </c>
-      <c r="J3" s="62" t="s">
+      <c r="K3" s="62" t="s">
         <v>660</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="L3" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="M3" s="50" t="s">
         <v>661</v>
       </c>
-      <c r="M3" s="57"/>
       <c r="N3" s="57"/>
-      <c r="O3" s="57" t="s">
+      <c r="O3" s="57"/>
+      <c r="P3" s="57" t="s">
         <v>662</v>
       </c>
-      <c r="P3" s="50" t="s">
+      <c r="Q3" s="50" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="4" ht="74" customHeight="1" spans="1:16">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="50" t="s">
+    <row r="4" ht="74" customHeight="1" spans="2:17">
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="50" t="s">
         <v>663</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="E4" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="F4" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="G4" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="H4" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="I4" s="57" t="s">
         <v>80</v>
-      </c>
-      <c r="I4" s="63" t="s">
-        <v>50</v>
       </c>
       <c r="J4" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="58" t="s">
+      <c r="K4" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="58" t="s">
         <v>664</v>
       </c>
-      <c r="L4" s="50" t="s">
+      <c r="M4" s="50" t="s">
         <v>665</v>
       </c>
-      <c r="M4" s="57"/>
       <c r="N4" s="57"/>
       <c r="O4" s="57"/>
-      <c r="P4" s="57" t="s">
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:16">
-      <c r="A5" s="64"/>
+    <row r="5" ht="60" customHeight="1" spans="2:17">
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
@@ -18293,12 +18370,12 @@
       <c r="N5" s="64"/>
       <c r="O5" s="64"/>
       <c r="P5" s="64"/>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:16">
-      <c r="A6" s="65" t="s">
+      <c r="Q5" s="64"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="2:17">
+      <c r="B6" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="66"/>
       <c r="C6" s="66"/>
       <c r="D6" s="66"/>
       <c r="E6" s="66"/>
@@ -18313,137 +18390,137 @@
       <c r="N6" s="66"/>
       <c r="O6" s="66"/>
       <c r="P6" s="66"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:16">
-      <c r="A7" s="67" t="s">
+      <c r="Q6" s="66"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:17">
+      <c r="B7" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="C7" s="50" t="s">
         <v>666</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="D7" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="E7" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="69">
+      <c r="F7" s="69">
         <v>1</v>
       </c>
-      <c r="F7" s="44">
+      <c r="G7" s="44">
         <v>2</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="H7" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H7" s="69">
+      <c r="I7" s="69">
         <v>1</v>
-      </c>
-      <c r="I7" s="70">
-        <v>4</v>
       </c>
       <c r="J7" s="70">
         <v>4</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="70">
+        <v>4</v>
+      </c>
+      <c r="L7" s="69">
         <v>1</v>
       </c>
-      <c r="L7" s="68" t="s">
+      <c r="M7" s="68" t="s">
         <v>412</v>
       </c>
-      <c r="M7" s="68"/>
       <c r="N7" s="68"/>
-      <c r="O7" s="71">
+      <c r="O7" s="68"/>
+      <c r="P7" s="71">
         <v>1</v>
       </c>
-      <c r="P7" s="68" t="s">
+      <c r="Q7" s="68" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:16">
-      <c r="A8" s="72"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="50" t="s">
+    <row r="8" ht="24" customHeight="1" spans="2:17">
+      <c r="B8" s="72"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="E8" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="F8" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="G8" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="H8" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="I8" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="I8" s="73" t="s">
+      <c r="J8" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="73" t="s">
+      <c r="K8" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="50" t="s">
+      <c r="L8" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L8" s="50" t="s">
+      <c r="M8" s="50" t="s">
         <v>489</v>
       </c>
-      <c r="M8" s="68"/>
       <c r="N8" s="68"/>
-      <c r="O8" s="68" t="s">
+      <c r="O8" s="68"/>
+      <c r="P8" s="68" t="s">
         <v>668</v>
       </c>
-      <c r="P8" s="50" t="s">
+      <c r="Q8" s="50" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="9" ht="43.35" customHeight="1" spans="1:16">
-      <c r="A9" s="72"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="50" t="s">
+    <row r="9" ht="43.35" customHeight="1" spans="2:17">
+      <c r="B9" s="72"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="E9" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="F9" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="G9" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="H9" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="74" t="s">
+      <c r="I9" s="74" t="s">
         <v>84</v>
-      </c>
-      <c r="I9" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J9" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="69" t="s">
+      <c r="K9" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="69" t="s">
         <v>664</v>
       </c>
-      <c r="L9" s="76" t="s">
+      <c r="M9" s="76" t="s">
         <v>670</v>
       </c>
-      <c r="M9" s="76"/>
       <c r="N9" s="76"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="68" t="s">
+      <c r="O9" s="76"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="68" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" s="52" customFormat="1" ht="60" customHeight="1" spans="1:16">
-      <c r="A10" s="77"/>
+    <row r="10" s="52" customFormat="1" ht="60" customHeight="1" spans="2:17">
       <c r="B10" s="77"/>
       <c r="C10" s="77"/>
       <c r="D10" s="77"/>
@@ -18459,13 +18536,13 @@
       <c r="N10" s="77"/>
       <c r="O10" s="77"/>
       <c r="P10" s="77"/>
-    </row>
-    <row r="11" s="52" customFormat="1" ht="30" customHeight="1" spans="1:16">
-      <c r="A11" s="65" t="s">
+      <c r="Q10" s="77"/>
+    </row>
+    <row r="11" s="52" customFormat="1" ht="30" customHeight="1" spans="2:17">
+      <c r="B11" s="65" t="s">
         <v>671</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="78"/>
+      <c r="C11" s="66"/>
       <c r="D11" s="78"/>
       <c r="E11" s="78"/>
       <c r="F11" s="78"/>
@@ -18473,49 +18550,47 @@
       <c r="H11" s="78"/>
       <c r="I11" s="78"/>
       <c r="J11" s="78"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="79"/>
       <c r="M11" s="78"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="78"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:16">
-      <c r="A12" s="67" t="s">
+      <c r="O11" s="78"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="78"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="2:17">
+      <c r="B12" s="67" t="s">
         <v>672</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="C12" s="50" t="s">
         <v>666</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="D12" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="E12" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="69">
+      <c r="F12" s="69">
         <v>1</v>
       </c>
-      <c r="F12" s="44">
+      <c r="G12" s="44">
         <v>2</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="H12" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H12" s="69">
+      <c r="I12" s="69">
         <v>1</v>
-      </c>
-      <c r="I12" s="70">
-        <v>4</v>
       </c>
       <c r="J12" s="70">
         <v>4</v>
       </c>
-      <c r="K12" s="69">
+      <c r="K12" s="70">
+        <v>4</v>
+      </c>
+      <c r="L12" s="69">
         <v>1</v>
-      </c>
-      <c r="L12" s="68" t="s">
-        <v>202</v>
       </c>
       <c r="M12" s="68" t="s">
         <v>202</v>
@@ -18523,91 +18598,91 @@
       <c r="N12" s="68" t="s">
         <v>202</v>
       </c>
-      <c r="O12" s="68">
+      <c r="O12" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="P12" s="68">
         <v>1</v>
       </c>
-      <c r="P12" s="68">
+      <c r="Q12" s="68">
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:16">
-      <c r="A13" s="72"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="50" t="s">
+    <row r="13" ht="24" customHeight="1" spans="2:17">
+      <c r="B13" s="72"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="E13" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="F13" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="G13" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="50" t="s">
+      <c r="H13" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="I13" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="I13" s="73" t="s">
+      <c r="J13" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="73" t="s">
+      <c r="K13" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="50" t="s">
+      <c r="L13" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L13" s="50" t="s">
+      <c r="M13" s="50" t="s">
         <v>673</v>
       </c>
-      <c r="M13" s="50" t="s">
+      <c r="N13" s="50" t="s">
         <v>497</v>
       </c>
-      <c r="N13" s="50" t="s">
+      <c r="O13" s="50" t="s">
         <v>500</v>
       </c>
-      <c r="O13" s="68" t="s">
+      <c r="P13" s="68" t="s">
         <v>668</v>
       </c>
-      <c r="P13" s="50" t="s">
+      <c r="Q13" s="50" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:16">
-      <c r="A14" s="72"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="50" t="s">
+    <row r="14" ht="24" customHeight="1" spans="2:17">
+      <c r="B14" s="72"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D14" s="74" t="s">
+      <c r="E14" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="68" t="s">
+      <c r="F14" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="G14" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="H14" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="74" t="s">
+      <c r="I14" s="74" t="s">
         <v>88</v>
-      </c>
-      <c r="I14" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J14" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="68" t="s">
+      <c r="K14" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="68" t="s">
         <v>674</v>
-      </c>
-      <c r="L14" s="68" t="s">
-        <v>675</v>
       </c>
       <c r="M14" s="68" t="s">
         <v>675</v>
@@ -18615,13 +18690,15 @@
       <c r="N14" s="68" t="s">
         <v>675</v>
       </c>
-      <c r="O14" s="68"/>
-      <c r="P14" s="68" t="s">
+      <c r="O14" s="68" t="s">
+        <v>675</v>
+      </c>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:16">
-      <c r="A15" s="64"/>
+    <row r="15" ht="60" customHeight="1" spans="2:17">
       <c r="B15" s="64"/>
       <c r="C15" s="64"/>
       <c r="D15" s="64"/>
@@ -18637,12 +18714,12 @@
       <c r="N15" s="64"/>
       <c r="O15" s="64"/>
       <c r="P15" s="64"/>
-    </row>
-    <row r="16" ht="27.95" customHeight="1" spans="1:16">
-      <c r="A16" s="80" t="s">
+      <c r="Q15" s="64"/>
+    </row>
+    <row r="16" ht="27.95" customHeight="1" spans="2:17">
+      <c r="B16" s="80" t="s">
         <v>676</v>
       </c>
-      <c r="B16" s="80"/>
       <c r="C16" s="80"/>
       <c r="D16" s="80"/>
       <c r="E16" s="80"/>
@@ -18657,146 +18734,146 @@
       <c r="N16" s="80"/>
       <c r="O16" s="80"/>
       <c r="P16" s="80"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:16">
-      <c r="A17" s="62" t="s">
+      <c r="Q16" s="80"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="2:17">
+      <c r="B17" s="62" t="s">
         <v>677</v>
       </c>
-      <c r="B17" s="73" t="s">
+      <c r="C17" s="73" t="s">
         <v>678</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="D17" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="E17" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E17" s="69">
+      <c r="F17" s="69">
         <v>1</v>
       </c>
-      <c r="F17" s="44">
+      <c r="G17" s="44">
         <v>2</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="H17" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H17" s="81">
+      <c r="I17" s="81">
         <v>1</v>
-      </c>
-      <c r="I17" s="70">
-        <v>4</v>
       </c>
       <c r="J17" s="70">
         <v>4</v>
       </c>
-      <c r="K17" s="81">
+      <c r="K17" s="70">
+        <v>4</v>
+      </c>
+      <c r="L17" s="81">
         <v>1</v>
       </c>
-      <c r="L17" s="75">
+      <c r="M17" s="75">
         <v>1</v>
       </c>
-      <c r="M17" s="81" t="s">
+      <c r="N17" s="81" t="s">
         <v>202</v>
       </c>
-      <c r="N17" s="70"/>
-      <c r="O17" s="68">
+      <c r="O17" s="70"/>
+      <c r="P17" s="68">
         <v>1</v>
       </c>
-      <c r="P17" s="68">
+      <c r="Q17" s="68">
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:16">
-      <c r="A18" s="82"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="50" t="s">
+    <row r="18" ht="24" customHeight="1" spans="2:17">
+      <c r="B18" s="82"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="E18" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="F18" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F18" s="48" t="s">
+      <c r="G18" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="50" t="s">
+      <c r="H18" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H18" s="62" t="s">
+      <c r="I18" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="I18" s="73" t="s">
+      <c r="J18" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="73" t="s">
+      <c r="K18" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="62" t="s">
+      <c r="L18" s="62" t="s">
         <v>167</v>
       </c>
-      <c r="L18" s="83" t="s">
+      <c r="M18" s="83" t="s">
         <v>679</v>
       </c>
-      <c r="M18" s="62" t="s">
+      <c r="N18" s="62" t="s">
         <v>673</v>
       </c>
-      <c r="N18" s="75"/>
-      <c r="O18" s="75" t="s">
+      <c r="O18" s="75"/>
+      <c r="P18" s="75" t="s">
         <v>668</v>
       </c>
-      <c r="P18" s="62" t="s">
+      <c r="Q18" s="62" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:16">
-      <c r="A19" s="82"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="50" t="s">
+    <row r="19" ht="24" customHeight="1" spans="2:17">
+      <c r="B19" s="82"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="E19" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="68" t="s">
+      <c r="F19" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="G19" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="H19" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="71" t="s">
+      <c r="I19" s="71" t="s">
         <v>105</v>
-      </c>
-      <c r="I19" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J19" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K19" s="71" t="s">
+      <c r="K19" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="L19" s="75" t="s">
+      <c r="M19" s="75" t="s">
         <v>680</v>
       </c>
-      <c r="M19" s="71" t="s">
+      <c r="N19" s="71" t="s">
         <v>675</v>
       </c>
-      <c r="N19" s="69"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="75" t="s">
+      <c r="O19" s="69"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="75" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:16">
-      <c r="A20" s="50" t="s">
+    <row r="20" ht="24" customHeight="1" spans="2:17">
+      <c r="B20" s="50" t="s">
         <v>681</v>
       </c>
-      <c r="B20" s="68"/>
       <c r="C20" s="68"/>
       <c r="D20" s="68"/>
       <c r="E20" s="68"/>
@@ -18811,9 +18888,9 @@
       <c r="N20" s="68"/>
       <c r="O20" s="68"/>
       <c r="P20" s="68"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:16">
-      <c r="A21" s="84"/>
+      <c r="Q20" s="68"/>
+    </row>
+    <row r="21" customHeight="1" spans="2:17">
       <c r="B21" s="84"/>
       <c r="C21" s="84"/>
       <c r="D21" s="84"/>
@@ -18828,12 +18905,12 @@
       <c r="M21" s="84"/>
       <c r="N21" s="84"/>
       <c r="O21" s="84"/>
-    </row>
-    <row r="23" ht="30" customHeight="1" spans="1:16">
-      <c r="A23" s="85" t="s">
+      <c r="P21" s="84"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="2:17">
+      <c r="B23" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="79"/>
       <c r="C23" s="79"/>
       <c r="D23" s="79"/>
       <c r="E23" s="79"/>
@@ -18847,42 +18924,40 @@
       <c r="M23" s="79"/>
       <c r="N23" s="79"/>
       <c r="O23" s="79"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:16">
-      <c r="A24" s="67" t="s">
+      <c r="P23" s="79"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:17">
+      <c r="B24" s="67" t="s">
         <v>682</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="C24" s="50" t="s">
         <v>666</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="D24" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="E24" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="69">
+      <c r="F24" s="69">
         <v>1</v>
       </c>
-      <c r="F24" s="44">
+      <c r="G24" s="44">
         <v>2</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="H24" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H24" s="69">
+      <c r="I24" s="69">
         <v>1</v>
-      </c>
-      <c r="I24" s="70">
-        <v>4</v>
       </c>
       <c r="J24" s="70">
         <v>4</v>
       </c>
-      <c r="K24" s="69">
-        <v>1</v>
-      </c>
-      <c r="L24" s="68">
+      <c r="K24" s="70">
+        <v>4</v>
+      </c>
+      <c r="L24" s="69">
         <v>1</v>
       </c>
       <c r="M24" s="68">
@@ -18891,96 +18966,98 @@
       <c r="N24" s="68">
         <v>1</v>
       </c>
-      <c r="O24" s="68" t="s">
+      <c r="O24" s="68">
+        <v>1</v>
+      </c>
+      <c r="P24" s="68" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1" spans="1:16">
-      <c r="A25" s="71"/>
+    <row r="25" ht="24" customHeight="1" spans="2:17">
       <c r="B25" s="71"/>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="71"/>
+      <c r="D25" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="E25" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="F25" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="G25" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="50" t="s">
+      <c r="H25" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="I25" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="I25" s="73" t="s">
+      <c r="J25" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J25" s="73" t="s">
+      <c r="K25" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K25" s="50" t="s">
+      <c r="L25" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L25" s="50" t="s">
+      <c r="M25" s="50" t="s">
         <v>683</v>
       </c>
-      <c r="M25" s="50" t="s">
+      <c r="N25" s="50" t="s">
         <v>684</v>
       </c>
-      <c r="N25" s="68" t="s">
+      <c r="O25" s="68" t="s">
         <v>668</v>
       </c>
-      <c r="O25" s="50" t="s">
+      <c r="P25" s="50" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1" spans="1:16">
-      <c r="A26" s="71"/>
+    <row r="26" ht="24" customHeight="1" spans="2:17">
       <c r="B26" s="71"/>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="71"/>
+      <c r="D26" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D26" s="74" t="s">
+      <c r="E26" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="F26" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="G26" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="68" t="s">
+      <c r="H26" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H26" s="68" t="s">
+      <c r="I26" s="68" t="s">
         <v>101</v>
-      </c>
-      <c r="I26" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J26" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K26" s="68" t="s">
+      <c r="K26" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L26" s="68" t="s">
         <v>102</v>
-      </c>
-      <c r="L26" s="68" t="s">
-        <v>664</v>
       </c>
       <c r="M26" s="68" t="s">
         <v>664</v>
       </c>
-      <c r="N26" s="71"/>
-      <c r="O26" s="68" t="s">
+      <c r="N26" s="68" t="s">
+        <v>664</v>
+      </c>
+      <c r="O26" s="71"/>
+      <c r="P26" s="68" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1" spans="1:16">
-      <c r="A27" s="64"/>
+    <row r="27" ht="60" customHeight="1" spans="2:17">
       <c r="B27" s="64"/>
       <c r="C27" s="64"/>
       <c r="D27" s="64"/>
@@ -18995,12 +19072,12 @@
       <c r="M27" s="64"/>
       <c r="N27" s="64"/>
       <c r="O27" s="64"/>
-    </row>
-    <row r="28" ht="30" customHeight="1" spans="1:16">
-      <c r="A28" s="65" t="s">
+      <c r="P27" s="64"/>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="2:17">
+      <c r="B28" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="66"/>
       <c r="C28" s="66"/>
       <c r="D28" s="66"/>
       <c r="E28" s="66"/>
@@ -19014,143 +19091,143 @@
       <c r="M28" s="66"/>
       <c r="N28" s="66"/>
       <c r="O28" s="66"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:16">
-      <c r="A29" s="67" t="s">
+      <c r="P28" s="66"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:17">
+      <c r="B29" s="67" t="s">
         <v>685</v>
       </c>
-      <c r="B29" s="50" t="s">
+      <c r="C29" s="50" t="s">
         <v>666</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="D29" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="68" t="s">
+      <c r="E29" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E29" s="69">
+      <c r="F29" s="69">
         <v>1</v>
       </c>
-      <c r="F29" s="44">
+      <c r="G29" s="44">
         <v>2</v>
       </c>
-      <c r="G29" s="68" t="s">
+      <c r="H29" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H29" s="69">
+      <c r="I29" s="69">
         <v>1</v>
-      </c>
-      <c r="I29" s="70">
-        <v>4</v>
       </c>
       <c r="J29" s="70">
         <v>4</v>
       </c>
-      <c r="K29" s="69">
-        <v>1</v>
-      </c>
-      <c r="L29" s="68">
+      <c r="K29" s="70">
+        <v>4</v>
+      </c>
+      <c r="L29" s="69">
         <v>1</v>
       </c>
       <c r="M29" s="68">
         <v>1</v>
       </c>
-      <c r="N29" s="71">
+      <c r="N29" s="68">
         <v>1</v>
       </c>
-      <c r="O29" s="68" t="s">
+      <c r="O29" s="71">
+        <v>1</v>
+      </c>
+      <c r="P29" s="68" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1" spans="1:16">
-      <c r="A30" s="72"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="50" t="s">
+    <row r="30" ht="24" customHeight="1" spans="2:17">
+      <c r="B30" s="72"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D30" s="50" t="s">
+      <c r="E30" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E30" s="50" t="s">
+      <c r="F30" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="G30" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G30" s="50" t="s">
+      <c r="H30" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H30" s="50" t="s">
+      <c r="I30" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="I30" s="73" t="s">
+      <c r="J30" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="73" t="s">
+      <c r="K30" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K30" s="50" t="s">
+      <c r="L30" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L30" s="50" t="s">
+      <c r="M30" s="50" t="s">
         <v>683</v>
       </c>
-      <c r="M30" s="50" t="s">
+      <c r="N30" s="50" t="s">
         <v>684</v>
       </c>
-      <c r="N30" s="68" t="s">
+      <c r="O30" s="68" t="s">
         <v>668</v>
       </c>
-      <c r="O30" s="50" t="s">
+      <c r="P30" s="50" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:16">
-      <c r="A31" s="72"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="50" t="s">
+    <row r="31" ht="24" customHeight="1" spans="2:17">
+      <c r="B31" s="72"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D31" s="74" t="s">
+      <c r="E31" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="68" t="s">
+      <c r="F31" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="G31" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="H31" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="68" t="s">
+      <c r="I31" s="68" t="s">
         <v>114</v>
-      </c>
-      <c r="I31" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J31" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K31" s="68" t="s">
+      <c r="K31" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L31" s="68" t="s">
         <v>102</v>
-      </c>
-      <c r="L31" s="68" t="s">
-        <v>664</v>
       </c>
       <c r="M31" s="68" t="s">
         <v>664</v>
       </c>
-      <c r="N31" s="71"/>
-      <c r="O31" s="68" t="s">
+      <c r="N31" s="68" t="s">
+        <v>664</v>
+      </c>
+      <c r="O31" s="71"/>
+      <c r="P31" s="68" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1" spans="1:16">
-      <c r="A32" s="50" t="s">
+    <row r="32" ht="24" customHeight="1" spans="2:17">
+      <c r="B32" s="50" t="s">
         <v>686</v>
       </c>
-      <c r="B32" s="68"/>
       <c r="C32" s="68"/>
       <c r="D32" s="68"/>
       <c r="E32" s="68"/>
@@ -19164,9 +19241,9 @@
       <c r="M32" s="68"/>
       <c r="N32" s="68"/>
       <c r="O32" s="68"/>
-    </row>
-    <row r="33" ht="33" customHeight="1" spans="1:17">
-      <c r="A33" s="86"/>
+      <c r="P32" s="68"/>
+    </row>
+    <row r="33" ht="33" customHeight="1" spans="2:18">
       <c r="B33" s="86"/>
       <c r="C33" s="86"/>
       <c r="D33" s="86"/>
@@ -19181,13 +19258,13 @@
       <c r="M33" s="86"/>
       <c r="N33" s="86"/>
       <c r="O33" s="86"/>
+      <c r="P33" s="86"/>
     </row>
     <row r="34" ht="29" customHeight="1"/>
-    <row r="35" ht="26.1" customHeight="1" spans="1:17">
-      <c r="A35" s="87" t="s">
+    <row r="35" ht="26.1" customHeight="1" spans="2:18">
+      <c r="B35" s="87" t="s">
         <v>687</v>
       </c>
-      <c r="B35" s="88"/>
       <c r="C35" s="88"/>
       <c r="D35" s="88"/>
       <c r="E35" s="88"/>
@@ -19202,152 +19279,152 @@
       <c r="N35" s="88"/>
       <c r="O35" s="88"/>
       <c r="P35" s="88"/>
-    </row>
-    <row r="36" ht="27.95" customHeight="1" spans="1:17">
-      <c r="A36" s="89" t="s">
+      <c r="Q35" s="88"/>
+    </row>
+    <row r="36" ht="27.95" customHeight="1" spans="2:18">
+      <c r="B36" s="89" t="s">
         <v>687</v>
       </c>
-      <c r="B36" s="50" t="s">
+      <c r="C36" s="50" t="s">
         <v>657</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="D36" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="E36" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="E36" s="58">
+      <c r="F36" s="58">
         <v>1</v>
       </c>
-      <c r="F36" s="44">
+      <c r="G36" s="44">
         <v>2</v>
       </c>
-      <c r="G36" s="57" t="s">
+      <c r="H36" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="H36" s="58">
+      <c r="I36" s="58">
         <v>1</v>
-      </c>
-      <c r="I36" s="59">
-        <v>4</v>
       </c>
       <c r="J36" s="59">
         <v>4</v>
       </c>
-      <c r="K36" s="57" t="s">
+      <c r="K36" s="59">
+        <v>4</v>
+      </c>
+      <c r="L36" s="57" t="s">
         <v>412</v>
       </c>
-      <c r="L36" s="50" t="s">
+      <c r="M36" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="M36" s="57"/>
       <c r="N36" s="57"/>
-      <c r="O36" s="57">
+      <c r="O36" s="57"/>
+      <c r="P36" s="57">
         <v>1</v>
       </c>
-      <c r="P36" s="57">
+      <c r="Q36" s="57">
         <v>2</v>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1" spans="1:17">
-      <c r="A37" s="60"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="50" t="s">
+    <row r="37" ht="24" customHeight="1" spans="2:18">
+      <c r="B37" s="60"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D37" s="50" t="s">
+      <c r="E37" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="F37" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F37" s="48" t="s">
+      <c r="G37" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="50" t="s">
+      <c r="H37" s="50" t="s">
         <v>658</v>
       </c>
-      <c r="H37" s="50" t="s">
+      <c r="I37" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="I37" s="62" t="s">
+      <c r="J37" s="62" t="s">
         <v>659</v>
       </c>
-      <c r="J37" s="62" t="s">
+      <c r="K37" s="62" t="s">
         <v>660</v>
       </c>
-      <c r="K37" s="50" t="s">
+      <c r="L37" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L37" s="89" t="s">
+      <c r="M37" s="89" t="s">
         <v>688</v>
       </c>
-      <c r="M37" s="57"/>
       <c r="N37" s="57"/>
-      <c r="O37" s="57" t="s">
+      <c r="O37" s="57"/>
+      <c r="P37" s="57" t="s">
         <v>662</v>
       </c>
-      <c r="P37" s="50" t="s">
+      <c r="Q37" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="Q37" s="68">
+      <c r="R37" s="68">
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="76" customHeight="1" spans="1:17">
-      <c r="A38" s="60"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="50" t="s">
+    <row r="38" ht="76" customHeight="1" spans="2:18">
+      <c r="B38" s="60"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="50" t="s">
         <v>663</v>
       </c>
-      <c r="D38" s="57" t="s">
+      <c r="E38" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="57" t="s">
+      <c r="F38" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="50" t="s">
+      <c r="G38" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G38" s="57" t="s">
+      <c r="H38" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H38" s="57" t="s">
+      <c r="I38" s="57" t="s">
         <v>118</v>
-      </c>
-      <c r="I38" s="63" t="s">
-        <v>50</v>
       </c>
       <c r="J38" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="K38" s="58" t="s">
+      <c r="K38" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="L38" s="58" t="s">
         <v>664</v>
       </c>
-      <c r="L38" s="89" t="s">
+      <c r="M38" s="89" t="s">
         <v>689</v>
       </c>
-      <c r="M38" s="57"/>
       <c r="N38" s="57"/>
       <c r="O38" s="57"/>
-      <c r="P38" s="57" t="s">
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="Q38" s="62" t="s">
+      <c r="R38" s="62" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="1:17">
-      <c r="Q39" s="75" t="s">
+    <row r="39" ht="24" customHeight="1" spans="2:18">
+      <c r="R39" s="75" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1"/>
-    <row r="41" customHeight="1" spans="1:17">
-      <c r="A41" s="80" t="s">
+    <row r="41" customHeight="1" spans="2:18">
+      <c r="B41" s="80" t="s">
         <v>122</v>
       </c>
-      <c r="B41" s="80"/>
       <c r="C41" s="80"/>
       <c r="D41" s="80"/>
       <c r="E41" s="80"/>
@@ -19361,163 +19438,163 @@
       <c r="M41" s="80"/>
       <c r="N41" s="80"/>
       <c r="O41" s="80"/>
-      <c r="P41" s="90"/>
-      <c r="Q41" s="91"/>
-    </row>
-    <row r="42" ht="32.25" customHeight="1" spans="1:17">
-      <c r="A42" s="62" t="s">
+      <c r="P41" s="80"/>
+      <c r="Q41" s="90"/>
+      <c r="R41" s="91"/>
+    </row>
+    <row r="42" ht="32.25" customHeight="1" spans="2:18">
+      <c r="B42" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B42" s="73" t="s">
+      <c r="C42" s="73" t="s">
         <v>678</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="D42" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="E42" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E42" s="69">
+      <c r="F42" s="69">
         <v>1</v>
       </c>
-      <c r="F42" s="44">
+      <c r="G42" s="44">
         <v>2</v>
       </c>
-      <c r="G42" s="68" t="s">
+      <c r="H42" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="81">
+      <c r="I42" s="81">
         <v>1</v>
-      </c>
-      <c r="I42" s="70">
-        <v>4</v>
       </c>
       <c r="J42" s="70">
         <v>4</v>
       </c>
-      <c r="K42" s="81">
+      <c r="K42" s="70">
+        <v>4</v>
+      </c>
+      <c r="L42" s="81">
         <v>1</v>
-      </c>
-      <c r="L42" s="75" t="s">
-        <v>158</v>
       </c>
       <c r="M42" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="N42" s="81">
+      <c r="N42" s="75" t="s">
+        <v>158</v>
+      </c>
+      <c r="O42" s="81">
         <v>2</v>
       </c>
-      <c r="O42" s="92">
+      <c r="P42" s="92">
         <v>2</v>
       </c>
-      <c r="P42" s="93">
+      <c r="Q42" s="93">
         <v>2</v>
       </c>
-      <c r="Q42" s="94">
+      <c r="R42" s="94">
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="27.75" customHeight="1" spans="1:17">
-      <c r="A43" s="82"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="50" t="s">
+    <row r="43" ht="27.75" customHeight="1" spans="2:18">
+      <c r="B43" s="82"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D43" s="50" t="s">
+      <c r="E43" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E43" s="50" t="s">
+      <c r="F43" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="48" t="s">
+      <c r="G43" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G43" s="50" t="s">
+      <c r="H43" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H43" s="62" t="s">
+      <c r="I43" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="I43" s="73" t="s">
+      <c r="J43" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J43" s="73" t="s">
+      <c r="K43" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K43" s="62" t="s">
+      <c r="L43" s="62" t="s">
         <v>167</v>
       </c>
-      <c r="L43" s="83" t="s">
+      <c r="M43" s="83" t="s">
         <v>690</v>
       </c>
-      <c r="M43" s="83" t="s">
+      <c r="N43" s="83" t="s">
         <v>691</v>
       </c>
-      <c r="N43" s="62" t="s">
+      <c r="O43" s="62" t="s">
         <v>692</v>
       </c>
-      <c r="O43" s="95" t="s">
+      <c r="P43" s="95" t="s">
         <v>558</v>
       </c>
-      <c r="P43" s="96" t="s">
+      <c r="Q43" s="96" t="s">
         <v>693</v>
       </c>
-      <c r="Q43" s="97" t="s">
+      <c r="R43" s="97" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="44" ht="24.75" customHeight="1" spans="1:17">
-      <c r="A44" s="82"/>
-      <c r="B44" s="73"/>
-      <c r="C44" s="50" t="s">
+    <row r="44" ht="24.75" customHeight="1" spans="2:18">
+      <c r="B44" s="82"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D44" s="74" t="s">
+      <c r="E44" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="68" t="s">
+      <c r="F44" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F44" s="50" t="s">
+      <c r="G44" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G44" s="68" t="s">
+      <c r="H44" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H44" s="71" t="s">
+      <c r="I44" s="71" t="s">
         <v>123</v>
-      </c>
-      <c r="I44" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J44" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K44" s="71" t="s">
+      <c r="K44" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L44" s="71" t="s">
         <v>694</v>
-      </c>
-      <c r="L44" s="75" t="s">
-        <v>695</v>
       </c>
       <c r="M44" s="75" t="s">
         <v>695</v>
       </c>
-      <c r="N44" s="71" t="s">
+      <c r="N44" s="75" t="s">
         <v>695</v>
       </c>
       <c r="O44" s="71" t="s">
         <v>695</v>
       </c>
-      <c r="P44" s="98" t="s">
+      <c r="P44" s="71" t="s">
         <v>695</v>
       </c>
-      <c r="Q44" s="91"/>
-    </row>
-    <row r="45" ht="31.5" customHeight="1" spans="1:17">
-      <c r="A45" s="50" t="s">
+      <c r="Q44" s="98" t="s">
+        <v>695</v>
+      </c>
+      <c r="R44" s="91"/>
+    </row>
+    <row r="45" ht="31.5" customHeight="1" spans="2:18">
+      <c r="B45" s="50" t="s">
         <v>696</v>
       </c>
-      <c r="B45" s="68"/>
       <c r="C45" s="68"/>
       <c r="D45" s="68"/>
       <c r="E45" s="68"/>
@@ -19531,15 +19608,15 @@
       <c r="M45" s="68"/>
       <c r="N45" s="68"/>
       <c r="O45" s="68"/>
-      <c r="P45" s="99"/>
-      <c r="Q45" s="91"/>
+      <c r="P45" s="68"/>
+      <c r="Q45" s="99"/>
+      <c r="R45" s="91"/>
     </row>
     <row r="46" ht="36" customHeight="1"/>
-    <row r="47" ht="37" customHeight="1" spans="1:17">
-      <c r="A47" s="80" t="s">
+    <row r="47" ht="37" customHeight="1" spans="2:18">
+      <c r="B47" s="80" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="80"/>
       <c r="C47" s="80"/>
       <c r="D47" s="80"/>
       <c r="E47" s="80"/>
@@ -19553,133 +19630,133 @@
       <c r="M47" s="80"/>
       <c r="N47" s="80"/>
       <c r="O47" s="80"/>
-      <c r="P47" s="100"/>
-    </row>
-    <row r="48" ht="34.5" customHeight="1" spans="1:17">
-      <c r="A48" s="62" t="s">
+      <c r="P47" s="80"/>
+      <c r="Q47" s="100"/>
+    </row>
+    <row r="48" ht="34.5" customHeight="1" spans="2:18">
+      <c r="B48" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="B48" s="73" t="s">
+      <c r="C48" s="73" t="s">
         <v>678</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="D48" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D48" s="68" t="s">
+      <c r="E48" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E48" s="69">
+      <c r="F48" s="69">
         <v>1</v>
       </c>
-      <c r="F48" s="44">
+      <c r="G48" s="44">
         <v>2</v>
       </c>
-      <c r="G48" s="68" t="s">
+      <c r="H48" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H48" s="81">
+      <c r="I48" s="81">
         <v>1</v>
-      </c>
-      <c r="I48" s="70">
-        <v>4</v>
       </c>
       <c r="J48" s="70">
         <v>4</v>
       </c>
-      <c r="K48" s="81">
+      <c r="K48" s="70">
+        <v>4</v>
+      </c>
+      <c r="L48" s="81">
         <v>1</v>
       </c>
-      <c r="L48" s="75" t="s">
+      <c r="M48" s="75" t="s">
         <v>412</v>
       </c>
-      <c r="M48" s="68">
+      <c r="N48" s="68">
         <v>1</v>
       </c>
-      <c r="N48" s="68">
+      <c r="O48" s="68">
         <v>2</v>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1" spans="1:16">
-      <c r="A49" s="82"/>
-      <c r="B49" s="73"/>
-      <c r="C49" s="50" t="s">
+    <row r="49" ht="30" customHeight="1" spans="2:17">
+      <c r="B49" s="82"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D49" s="50" t="s">
+      <c r="E49" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E49" s="50" t="s">
+      <c r="F49" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F49" s="48" t="s">
+      <c r="G49" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G49" s="50" t="s">
+      <c r="H49" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H49" s="62" t="s">
+      <c r="I49" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="I49" s="73" t="s">
+      <c r="J49" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J49" s="73" t="s">
+      <c r="K49" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K49" s="62" t="s">
+      <c r="L49" s="62" t="s">
         <v>167</v>
       </c>
-      <c r="L49" s="83" t="s">
+      <c r="M49" s="83" t="s">
         <v>697</v>
       </c>
-      <c r="M49" s="75" t="s">
+      <c r="N49" s="75" t="s">
         <v>668</v>
       </c>
-      <c r="N49" s="62" t="s">
+      <c r="O49" s="62" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="50" ht="93" customHeight="1" spans="1:16">
-      <c r="A50" s="82"/>
-      <c r="B50" s="73"/>
-      <c r="C50" s="50" t="s">
+    <row r="50" ht="93" customHeight="1" spans="2:17">
+      <c r="B50" s="82"/>
+      <c r="C50" s="73"/>
+      <c r="D50" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D50" s="74" t="s">
+      <c r="E50" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="68" t="s">
+      <c r="F50" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F50" s="50" t="s">
+      <c r="G50" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G50" s="68" t="s">
+      <c r="H50" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H50" s="71" t="s">
+      <c r="I50" s="71" t="s">
         <v>126</v>
-      </c>
-      <c r="I50" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J50" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K50" s="71" t="s">
+      <c r="K50" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L50" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="L50" s="101" t="s">
+      <c r="M50" s="101" t="s">
         <v>565</v>
       </c>
-      <c r="M50" s="71"/>
-      <c r="N50" s="75" t="s">
+      <c r="N50" s="71"/>
+      <c r="O50" s="75" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="51" ht="30.75" customHeight="1" spans="1:16">
-      <c r="A51" s="50"/>
-      <c r="B51" s="68"/>
+    <row r="51" ht="30.75" customHeight="1" spans="2:17">
+      <c r="B51" s="50"/>
       <c r="C51" s="68"/>
       <c r="D51" s="68"/>
       <c r="E51" s="68"/>
@@ -19693,14 +19770,14 @@
       <c r="M51" s="68"/>
       <c r="N51" s="68"/>
       <c r="O51" s="68"/>
-      <c r="P51" s="102"/>
+      <c r="P51" s="68"/>
+      <c r="Q51" s="102"/>
     </row>
     <row r="52" ht="42" customHeight="1"/>
-    <row r="53" ht="29.25" customHeight="1" spans="1:16">
-      <c r="A53" s="103" t="s">
+    <row r="53" ht="29.25" customHeight="1" spans="2:17">
+      <c r="B53" s="103" t="s">
         <v>698</v>
       </c>
-      <c r="B53" s="78"/>
       <c r="C53" s="78"/>
       <c r="D53" s="78"/>
       <c r="E53" s="78"/>
@@ -19714,137 +19791,137 @@
       <c r="M53" s="78"/>
       <c r="N53" s="78"/>
       <c r="O53" s="78"/>
-    </row>
-    <row r="54" ht="30.75" customHeight="1" spans="1:16">
-      <c r="A54" s="67" t="s">
+      <c r="P53" s="78"/>
+    </row>
+    <row r="54" ht="30.75" customHeight="1" spans="2:17">
+      <c r="B54" s="67" t="s">
         <v>699</v>
       </c>
-      <c r="B54" s="50" t="s">
+      <c r="C54" s="50" t="s">
         <v>666</v>
       </c>
-      <c r="C54" s="50" t="s">
+      <c r="D54" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D54" s="68" t="s">
+      <c r="E54" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E54" s="69">
+      <c r="F54" s="69">
         <v>1</v>
       </c>
-      <c r="F54" s="44">
+      <c r="G54" s="44">
         <v>2</v>
       </c>
-      <c r="G54" s="68" t="s">
+      <c r="H54" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H54" s="69">
+      <c r="I54" s="69">
         <v>7</v>
-      </c>
-      <c r="I54" s="70">
-        <v>4</v>
       </c>
       <c r="J54" s="70">
         <v>4</v>
       </c>
-      <c r="K54" s="69">
+      <c r="K54" s="70">
+        <v>4</v>
+      </c>
+      <c r="L54" s="69">
         <v>8</v>
       </c>
-      <c r="L54" s="50" t="s">
+      <c r="M54" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="M54" s="68"/>
-      <c r="N54" s="71">
+      <c r="N54" s="68"/>
+      <c r="O54" s="71">
         <v>1</v>
       </c>
-      <c r="O54" s="71">
+      <c r="P54" s="71">
         <v>2</v>
       </c>
     </row>
-    <row r="55" ht="32.25" customHeight="1" spans="1:16">
-      <c r="A55" s="71"/>
+    <row r="55" ht="32.25" customHeight="1" spans="2:17">
       <c r="B55" s="71"/>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="71"/>
+      <c r="D55" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="D55" s="50" t="s">
+      <c r="E55" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="E55" s="50" t="s">
+      <c r="F55" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F55" s="48" t="s">
+      <c r="G55" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G55" s="50" t="s">
+      <c r="H55" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="H55" s="50" t="s">
+      <c r="I55" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="I55" s="73" t="s">
+      <c r="J55" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J55" s="73" t="s">
+      <c r="K55" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K55" s="50" t="s">
+      <c r="L55" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L55" s="50" t="s">
+      <c r="M55" s="50" t="s">
         <v>700</v>
       </c>
-      <c r="M55" s="68"/>
-      <c r="N55" s="68" t="s">
+      <c r="N55" s="68"/>
+      <c r="O55" s="68" t="s">
         <v>668</v>
       </c>
-      <c r="O55" s="50" t="s">
+      <c r="P55" s="50" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="56" ht="37.5" customHeight="1" spans="1:16">
-      <c r="A56" s="71"/>
+    <row r="56" ht="37.5" customHeight="1" spans="2:17">
       <c r="B56" s="71"/>
-      <c r="C56" s="50" t="s">
+      <c r="C56" s="71"/>
+      <c r="D56" s="50" t="s">
         <v>669</v>
       </c>
-      <c r="D56" s="74" t="s">
+      <c r="E56" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E56" s="68" t="s">
+      <c r="F56" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F56" s="50" t="s">
+      <c r="G56" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="H56" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H56" s="68" t="s">
+      <c r="I56" s="68" t="s">
         <v>129</v>
-      </c>
-      <c r="I56" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J56" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K56" s="69" t="s">
+      <c r="K56" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L56" s="69" t="s">
         <v>664</v>
       </c>
-      <c r="L56" s="50" t="s">
+      <c r="M56" s="50" t="s">
         <v>701</v>
       </c>
-      <c r="M56" s="68"/>
-      <c r="N56" s="71"/>
-      <c r="O56" s="68" t="s">
+      <c r="N56" s="68"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="68" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" s="53" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A59" s="104" t="s">
+    <row r="59" s="53" customFormat="1" customHeight="1" spans="2:17">
+      <c r="B59" s="104" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="105"/>
       <c r="C59" s="105"/>
       <c r="D59" s="105"/>
       <c r="E59" s="105"/>
@@ -19857,144 +19934,144 @@
       <c r="L59" s="105"/>
       <c r="M59" s="105"/>
       <c r="N59" s="105"/>
-      <c r="O59" s="106"/>
-    </row>
-    <row r="60" s="53" customFormat="1" ht="32.25" customHeight="1" spans="1:16">
-      <c r="A60" s="62" t="s">
+      <c r="O59" s="105"/>
+      <c r="P59" s="106"/>
+    </row>
+    <row r="60" s="53" customFormat="1" ht="32.25" customHeight="1" spans="2:17">
+      <c r="B60" s="62" t="s">
         <v>702</v>
       </c>
-      <c r="B60" s="73" t="s">
+      <c r="C60" s="73" t="s">
         <v>678</v>
       </c>
-      <c r="C60" s="68" t="s">
+      <c r="D60" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="68" t="s">
+      <c r="E60" s="68" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="69">
+      <c r="F60" s="69">
         <v>1</v>
       </c>
-      <c r="F60" s="44">
+      <c r="G60" s="44">
         <v>2</v>
       </c>
-      <c r="G60" s="68" t="s">
+      <c r="H60" s="68" t="s">
         <v>159</v>
       </c>
-      <c r="H60" s="81">
+      <c r="I60" s="81">
         <v>1</v>
-      </c>
-      <c r="I60" s="70">
-        <v>4</v>
       </c>
       <c r="J60" s="70">
         <v>4</v>
       </c>
-      <c r="K60" s="81">
+      <c r="K60" s="70">
+        <v>4</v>
+      </c>
+      <c r="L60" s="81">
         <v>1</v>
-      </c>
-      <c r="L60" s="75" t="s">
-        <v>412</v>
       </c>
       <c r="M60" s="75" t="s">
         <v>412</v>
       </c>
-      <c r="N60" s="94">
+      <c r="N60" s="75" t="s">
+        <v>412</v>
+      </c>
+      <c r="O60" s="94">
         <v>1</v>
       </c>
-      <c r="O60" s="107">
+      <c r="P60" s="107">
         <v>2</v>
       </c>
     </row>
-    <row r="61" s="53" customFormat="1" ht="27.75" customHeight="1" spans="1:16">
-      <c r="A61" s="82"/>
-      <c r="B61" s="73"/>
-      <c r="C61" s="68" t="s">
+    <row r="61" s="53" customFormat="1" ht="27.75" customHeight="1" spans="2:17">
+      <c r="B61" s="82"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="D61" s="68" t="s">
+      <c r="E61" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="E61" s="68" t="s">
+      <c r="F61" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="F61" s="48" t="s">
+      <c r="G61" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="G61" s="68" t="s">
+      <c r="H61" s="68" t="s">
         <v>444</v>
       </c>
-      <c r="H61" s="75" t="s">
+      <c r="I61" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="I61" s="73" t="s">
+      <c r="J61" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="J61" s="73" t="s">
+      <c r="K61" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K61" s="75" t="s">
+      <c r="L61" s="75" t="s">
         <v>167</v>
       </c>
-      <c r="L61" s="83" t="s">
+      <c r="M61" s="83" t="s">
         <v>567</v>
       </c>
-      <c r="M61" s="83" t="s">
+      <c r="N61" s="83" t="s">
         <v>703</v>
       </c>
-      <c r="N61" s="97" t="s">
+      <c r="O61" s="97" t="s">
         <v>704</v>
       </c>
-      <c r="O61" s="108" t="s">
+      <c r="P61" s="108" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="62" s="53" customFormat="1" ht="24.75" customHeight="1" spans="1:16">
-      <c r="A62" s="82"/>
-      <c r="B62" s="73"/>
-      <c r="C62" s="68" t="s">
+    <row r="62" s="53" customFormat="1" ht="24.75" customHeight="1" spans="2:17">
+      <c r="B62" s="82"/>
+      <c r="C62" s="73"/>
+      <c r="D62" s="68" t="s">
         <v>705</v>
       </c>
-      <c r="D62" s="74" t="s">
+      <c r="E62" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="109" t="s">
+      <c r="F62" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="F62" s="50" t="s">
+      <c r="G62" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G62" s="68" t="s">
+      <c r="H62" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="H62" s="71" t="s">
+      <c r="I62" s="71" t="s">
         <v>131</v>
-      </c>
-      <c r="I62" s="75" t="s">
-        <v>50</v>
       </c>
       <c r="J62" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="K62" s="71" t="s">
+      <c r="K62" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L62" s="71" t="s">
         <v>76</v>
-      </c>
-      <c r="L62" s="75" t="s">
-        <v>695</v>
       </c>
       <c r="M62" s="75" t="s">
         <v>695</v>
       </c>
-      <c r="N62" s="91"/>
-      <c r="O62" s="108" t="s">
+      <c r="N62" s="75" t="s">
+        <v>695</v>
+      </c>
+      <c r="O62" s="91"/>
+      <c r="P62" s="108" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="65" ht="42" customHeight="1" spans="1:17">
-      <c r="A65" s="110" t="s">
+    <row r="65" ht="42" customHeight="1" spans="2:18">
+      <c r="B65" s="110" t="s">
         <v>706</v>
       </c>
-      <c r="B65" s="111"/>
       <c r="C65" s="111"/>
       <c r="D65" s="111"/>
       <c r="E65" s="111"/>
@@ -20004,154 +20081,154 @@
       <c r="I65" s="111"/>
       <c r="J65" s="111"/>
       <c r="K65" s="111"/>
-      <c r="L65" s="112"/>
+      <c r="L65" s="111"/>
       <c r="M65" s="112"/>
       <c r="N65" s="112"/>
       <c r="O65" s="112"/>
       <c r="P65" s="112"/>
-    </row>
-    <row r="66" ht="42" customHeight="1" spans="1:17">
-      <c r="A66" s="35" t="s">
+      <c r="Q65" s="112"/>
+    </row>
+    <row r="66" ht="42" customHeight="1" spans="2:18">
+      <c r="B66" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="B66" s="35" t="s">
+      <c r="C66" s="35" t="s">
         <v>707</v>
       </c>
-      <c r="C66" s="35" t="s">
+      <c r="D66" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="D66" s="113" t="s">
+      <c r="E66" s="113" t="s">
         <v>158</v>
       </c>
-      <c r="E66" s="114">
+      <c r="F66" s="114">
         <v>1</v>
       </c>
-      <c r="F66" s="27">
+      <c r="G66" s="27">
         <v>2</v>
       </c>
-      <c r="G66" s="113" t="s">
+      <c r="H66" s="113" t="s">
         <v>159</v>
       </c>
-      <c r="H66" s="114">
+      <c r="I66" s="114">
         <v>1</v>
-      </c>
-      <c r="I66" s="115">
-        <v>4</v>
       </c>
       <c r="J66" s="115">
         <v>4</v>
       </c>
-      <c r="K66" s="116" t="s">
+      <c r="K66" s="115">
+        <v>4</v>
+      </c>
+      <c r="L66" s="116" t="s">
         <v>412</v>
       </c>
-      <c r="L66" s="117">
+      <c r="M66" s="117">
         <v>1</v>
       </c>
-      <c r="M66" s="37" t="s">
+      <c r="N66" s="37" t="s">
         <v>412</v>
       </c>
-      <c r="N66" s="37" t="s">
+      <c r="O66" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="O66" s="118">
+      <c r="P66" s="118">
         <v>1</v>
       </c>
-      <c r="P66" s="118">
+      <c r="Q66" s="118">
         <v>2</v>
       </c>
     </row>
-    <row r="67" ht="42" customHeight="1" spans="1:17">
-      <c r="A67" s="119"/>
-      <c r="B67" s="120"/>
-      <c r="C67" s="35" t="s">
+    <row r="67" ht="42" customHeight="1" spans="2:18">
+      <c r="B67" s="119"/>
+      <c r="C67" s="120"/>
+      <c r="D67" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="D67" s="35" t="s">
+      <c r="E67" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="E67" s="35" t="s">
+      <c r="F67" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="F67" s="31" t="s">
+      <c r="G67" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="G67" s="35" t="s">
+      <c r="H67" s="35" t="s">
         <v>708</v>
       </c>
-      <c r="H67" s="35" t="s">
+      <c r="I67" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="I67" s="121" t="s">
+      <c r="J67" s="121" t="s">
         <v>709</v>
       </c>
-      <c r="J67" s="121" t="s">
+      <c r="K67" s="121" t="s">
         <v>710</v>
       </c>
-      <c r="K67" s="122" t="s">
+      <c r="L67" s="122" t="s">
         <v>167</v>
       </c>
-      <c r="L67" s="117" t="s">
+      <c r="M67" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="M67" s="37" t="s">
+      <c r="N67" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="N67" s="37" t="s">
+      <c r="O67" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="O67" s="118" t="s">
+      <c r="P67" s="118" t="s">
         <v>713</v>
       </c>
-      <c r="P67" s="37" t="s">
+      <c r="Q67" s="37" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="68" ht="292" customHeight="1" spans="1:17">
-      <c r="A68" s="119"/>
-      <c r="B68" s="120"/>
-      <c r="C68" s="35" t="s">
+    <row r="68" ht="292" customHeight="1" spans="2:18">
+      <c r="B68" s="119"/>
+      <c r="C68" s="120"/>
+      <c r="D68" s="35" t="s">
         <v>714</v>
       </c>
-      <c r="D68" s="113" t="s">
+      <c r="E68" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="E68" s="113" t="s">
+      <c r="F68" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="F68" s="35" t="s">
+      <c r="G68" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="G68" s="113" t="s">
+      <c r="H68" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="113" t="s">
+      <c r="I68" s="113" t="s">
         <v>134</v>
-      </c>
-      <c r="I68" s="123" t="s">
-        <v>50</v>
       </c>
       <c r="J68" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="K68" s="124" t="s">
+      <c r="K68" s="123" t="s">
+        <v>50</v>
+      </c>
+      <c r="L68" s="124" t="s">
         <v>664</v>
       </c>
-      <c r="L68" s="125" t="s">
+      <c r="M68" s="125" t="s">
         <v>715</v>
       </c>
-      <c r="M68" s="126" t="s">
+      <c r="N68" s="126" t="s">
         <v>716</v>
       </c>
-      <c r="N68" s="127" t="s">
+      <c r="O68" s="127" t="s">
         <v>717</v>
       </c>
-      <c r="O68" s="118"/>
-      <c r="P68" s="118" t="s">
+      <c r="P68" s="118"/>
+      <c r="Q68" s="118" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="70" s="53" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A70" s="128"/>
+    <row r="70" s="53" customFormat="1" customHeight="1" spans="2:18">
       <c r="B70" s="128"/>
       <c r="C70" s="128"/>
       <c r="D70" s="128"/>
@@ -20167,12 +20244,12 @@
       <c r="N70" s="128"/>
       <c r="O70" s="128"/>
       <c r="P70" s="128"/>
-    </row>
-    <row r="71" s="53" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A71" s="129" t="s">
+      <c r="Q70" s="128"/>
+    </row>
+    <row r="71" s="53" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B71" s="129" t="s">
         <v>718</v>
       </c>
-      <c r="B71" s="129"/>
       <c r="C71" s="129"/>
       <c r="D71" s="129"/>
       <c r="E71" s="129"/>
@@ -20187,161 +20264,161 @@
       <c r="N71" s="129"/>
       <c r="O71" s="129"/>
       <c r="P71" s="129"/>
-    </row>
-    <row r="72" s="54" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A72" s="130" t="s">
+      <c r="Q71" s="129"/>
+    </row>
+    <row r="72" s="54" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B72" s="130" t="s">
         <v>135</v>
       </c>
-      <c r="B72" s="131" t="s">
+      <c r="C72" s="131" t="s">
         <v>678</v>
       </c>
-      <c r="C72" s="132" t="s">
+      <c r="D72" s="132" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="133" t="s">
+      <c r="E72" s="133" t="s">
         <v>158</v>
       </c>
-      <c r="E72" s="134">
+      <c r="F72" s="134">
         <v>1</v>
       </c>
-      <c r="F72" s="135">
+      <c r="G72" s="135">
         <v>2</v>
       </c>
-      <c r="G72" s="133" t="s">
+      <c r="H72" s="133" t="s">
         <v>159</v>
       </c>
-      <c r="H72" s="136">
+      <c r="I72" s="136">
         <v>1</v>
-      </c>
-      <c r="I72" s="137">
-        <v>4</v>
       </c>
       <c r="J72" s="137">
         <v>4</v>
       </c>
-      <c r="K72" s="136">
+      <c r="K72" s="137">
+        <v>4</v>
+      </c>
+      <c r="L72" s="136">
         <v>1</v>
       </c>
-      <c r="L72" s="138" t="s">
+      <c r="M72" s="138" t="s">
         <v>202</v>
       </c>
-      <c r="M72" s="138" t="s">
+      <c r="N72" s="138" t="s">
         <v>412</v>
       </c>
-      <c r="N72" s="138">
+      <c r="O72" s="138">
         <v>1</v>
       </c>
-      <c r="O72" s="139" t="s">
+      <c r="P72" s="139" t="s">
         <v>202</v>
       </c>
-      <c r="P72" s="138">
+      <c r="Q72" s="138">
         <v>1</v>
       </c>
-      <c r="Q72" s="133">
+      <c r="R72" s="133">
         <v>2</v>
       </c>
     </row>
-    <row r="73" s="54" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A73" s="130"/>
-      <c r="B73" s="131"/>
-      <c r="C73" s="132" t="s">
+    <row r="73" s="54" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B73" s="130"/>
+      <c r="C73" s="131"/>
+      <c r="D73" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="D73" s="140" t="s">
+      <c r="E73" s="140" t="s">
         <v>161</v>
       </c>
-      <c r="E73" s="140" t="s">
+      <c r="F73" s="140" t="s">
         <v>162</v>
       </c>
-      <c r="F73" s="141" t="s">
+      <c r="G73" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="G73" s="142" t="s">
+      <c r="H73" s="142" t="s">
         <v>719</v>
       </c>
-      <c r="H73" s="130" t="s">
+      <c r="I73" s="130" t="s">
         <v>164</v>
       </c>
-      <c r="I73" s="143" t="s">
+      <c r="J73" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="J73" s="143" t="s">
+      <c r="K73" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="K73" s="130" t="s">
+      <c r="L73" s="130" t="s">
         <v>167</v>
       </c>
-      <c r="L73" s="139" t="s">
+      <c r="M73" s="139" t="s">
         <v>720</v>
       </c>
-      <c r="M73" s="139" t="s">
+      <c r="N73" s="139" t="s">
         <v>721</v>
       </c>
-      <c r="N73" s="139" t="s">
+      <c r="O73" s="139" t="s">
         <v>722</v>
       </c>
-      <c r="O73" s="139" t="s">
+      <c r="P73" s="139" t="s">
         <v>723</v>
       </c>
-      <c r="P73" s="138" t="s">
+      <c r="Q73" s="138" t="s">
         <v>724</v>
       </c>
-      <c r="Q73" s="130" t="s">
+      <c r="R73" s="130" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="74" s="54" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A74" s="144"/>
-      <c r="B74" s="145"/>
-      <c r="C74" s="146" t="s">
+    <row r="74" s="54" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B74" s="144"/>
+      <c r="C74" s="145"/>
+      <c r="D74" s="146" t="s">
         <v>725</v>
       </c>
-      <c r="D74" s="147" t="s">
+      <c r="E74" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="E74" s="148" t="s">
+      <c r="F74" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="F74" s="149" t="s">
+      <c r="G74" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="G74" s="148" t="s">
+      <c r="H74" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="H74" s="150" t="s">
+      <c r="I74" s="150" t="s">
         <v>136</v>
-      </c>
-      <c r="I74" s="151" t="s">
-        <v>50</v>
       </c>
       <c r="J74" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="K74" s="150">
+      <c r="K74" s="151" t="s">
+        <v>50</v>
+      </c>
+      <c r="L74" s="150">
         <v>10</v>
       </c>
-      <c r="L74" s="152">
+      <c r="M74" s="152">
         <v>115200</v>
       </c>
-      <c r="M74" s="153" t="s">
+      <c r="N74" s="153" t="s">
         <v>726</v>
       </c>
-      <c r="N74" s="154" t="s">
+      <c r="O74" s="154" t="s">
         <v>727</v>
       </c>
-      <c r="O74" s="155" t="s">
+      <c r="P74" s="155" t="s">
         <v>728</v>
       </c>
-      <c r="P74" s="156"/>
-      <c r="Q74" s="157" t="s">
+      <c r="Q74" s="156"/>
+      <c r="R74" s="157" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="75" s="53" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A75" s="158" t="s">
+    <row r="75" s="53" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B75" s="158" t="s">
         <v>729</v>
       </c>
-      <c r="B75" s="158"/>
       <c r="C75" s="158"/>
       <c r="D75" s="158"/>
       <c r="E75" s="158"/>
@@ -20356,9 +20433,9 @@
       <c r="N75" s="158"/>
       <c r="O75" s="158"/>
       <c r="P75" s="158"/>
-    </row>
-    <row r="76" s="53" customFormat="1" ht="23.1" customHeight="1" spans="1:17">
-      <c r="A76" s="159"/>
+      <c r="Q75" s="158"/>
+    </row>
+    <row r="76" s="53" customFormat="1" ht="23.1" customHeight="1" spans="2:18">
       <c r="B76" s="159"/>
       <c r="C76" s="159"/>
       <c r="D76" s="159"/>
@@ -20374,9 +20451,9 @@
       <c r="N76" s="159"/>
       <c r="O76" s="159"/>
       <c r="P76" s="159"/>
-    </row>
-    <row r="77" s="53" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A77" s="159"/>
+      <c r="Q76" s="159"/>
+    </row>
+    <row r="77" s="53" customFormat="1" ht="24" customHeight="1" spans="2:18">
       <c r="B77" s="159"/>
       <c r="C77" s="159"/>
       <c r="D77" s="159"/>
@@ -20392,12 +20469,12 @@
       <c r="N77" s="159"/>
       <c r="O77" s="159"/>
       <c r="P77" s="159"/>
-    </row>
-    <row r="78" s="53" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A78" s="160" t="s">
+      <c r="Q77" s="159"/>
+    </row>
+    <row r="78" s="53" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B78" s="160" t="s">
         <v>137</v>
       </c>
-      <c r="B78" s="160"/>
       <c r="C78" s="160"/>
       <c r="D78" s="160"/>
       <c r="E78" s="160"/>
@@ -20410,142 +20487,142 @@
       <c r="L78" s="160"/>
       <c r="M78" s="160"/>
       <c r="N78" s="160"/>
-      <c r="O78" s="161"/>
-      <c r="P78" s="159"/>
-    </row>
-    <row r="79" s="54" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A79" s="162" t="s">
+      <c r="O78" s="160"/>
+      <c r="P78" s="161"/>
+      <c r="Q78" s="159"/>
+    </row>
+    <row r="79" s="54" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B79" s="162" t="s">
         <v>137</v>
       </c>
-      <c r="B79" s="163" t="s">
+      <c r="C79" s="163" t="s">
         <v>730</v>
       </c>
-      <c r="C79" s="149" t="s">
+      <c r="D79" s="149" t="s">
         <v>157</v>
       </c>
-      <c r="D79" s="164" t="s">
+      <c r="E79" s="164" t="s">
         <v>158</v>
       </c>
-      <c r="E79" s="165">
+      <c r="F79" s="165">
         <v>1</v>
       </c>
-      <c r="F79" s="135">
+      <c r="G79" s="135">
         <v>2</v>
       </c>
-      <c r="G79" s="164" t="s">
+      <c r="H79" s="164" t="s">
         <v>159</v>
       </c>
-      <c r="H79" s="166">
+      <c r="I79" s="166">
         <v>1</v>
-      </c>
-      <c r="I79" s="167">
-        <v>4</v>
       </c>
       <c r="J79" s="167">
         <v>4</v>
       </c>
-      <c r="K79" s="166">
+      <c r="K79" s="167">
+        <v>4</v>
+      </c>
+      <c r="L79" s="166">
         <v>1</v>
       </c>
-      <c r="L79" s="168" t="s">
+      <c r="M79" s="168" t="s">
         <v>731</v>
       </c>
-      <c r="M79" s="138">
+      <c r="N79" s="138">
         <v>1</v>
       </c>
-      <c r="N79" s="133">
+      <c r="O79" s="133">
         <v>2</v>
       </c>
-      <c r="O79" s="169"/>
       <c r="P79" s="169"/>
-    </row>
-    <row r="80" s="54" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A80" s="162"/>
-      <c r="B80" s="163"/>
-      <c r="C80" s="149" t="s">
+      <c r="Q79" s="169"/>
+    </row>
+    <row r="80" s="54" customFormat="1" customHeight="1" spans="2:18">
+      <c r="B80" s="162"/>
+      <c r="C80" s="163"/>
+      <c r="D80" s="149" t="s">
         <v>160</v>
       </c>
-      <c r="D80" s="149" t="s">
+      <c r="E80" s="149" t="s">
         <v>161</v>
       </c>
-      <c r="E80" s="149" t="s">
+      <c r="F80" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="F80" s="141" t="s">
+      <c r="G80" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="G80" s="170" t="s">
+      <c r="H80" s="170" t="s">
         <v>719</v>
       </c>
-      <c r="H80" s="162" t="s">
+      <c r="I80" s="162" t="s">
         <v>164</v>
       </c>
-      <c r="I80" s="163" t="s">
+      <c r="J80" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="J80" s="163" t="s">
+      <c r="K80" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="K80" s="162" t="s">
+      <c r="L80" s="162" t="s">
         <v>167</v>
       </c>
-      <c r="L80" s="171" t="s">
+      <c r="M80" s="171" t="s">
         <v>732</v>
       </c>
-      <c r="M80" s="138" t="s">
+      <c r="N80" s="138" t="s">
         <v>724</v>
       </c>
-      <c r="N80" s="130" t="s">
+      <c r="O80" s="130" t="s">
         <v>170</v>
       </c>
-      <c r="O80" s="169"/>
       <c r="P80" s="169"/>
-    </row>
-    <row r="81" s="54" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A81" s="162"/>
-      <c r="B81" s="163"/>
-      <c r="C81" s="149" t="s">
+      <c r="Q80" s="169"/>
+    </row>
+    <row r="81" s="54" customFormat="1" customHeight="1" spans="2:20">
+      <c r="B81" s="162"/>
+      <c r="C81" s="163"/>
+      <c r="D81" s="149" t="s">
         <v>725</v>
       </c>
-      <c r="D81" s="172" t="s">
+      <c r="E81" s="172" t="s">
         <v>45</v>
       </c>
-      <c r="E81" s="164" t="s">
+      <c r="F81" s="164" t="s">
         <v>46</v>
       </c>
-      <c r="F81" s="149" t="s">
+      <c r="G81" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="G81" s="164" t="s">
+      <c r="H81" s="164" t="s">
         <v>48</v>
       </c>
-      <c r="H81" s="173" t="s">
+      <c r="I81" s="173" t="s">
         <v>138</v>
-      </c>
-      <c r="I81" s="174" t="s">
-        <v>50</v>
       </c>
       <c r="J81" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="K81" s="173" t="s">
+      <c r="K81" s="174" t="s">
+        <v>50</v>
+      </c>
+      <c r="L81" s="173" t="s">
         <v>731</v>
       </c>
-      <c r="L81" s="171" t="s">
+      <c r="M81" s="171" t="s">
         <v>733</v>
       </c>
-      <c r="M81" s="175"/>
-      <c r="N81" s="138" t="s">
+      <c r="N81" s="175"/>
+      <c r="O81" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="O81" s="169"/>
       <c r="P81" s="169"/>
-    </row>
-    <row r="82" s="53" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A82" s="140" t="s">
+      <c r="Q81" s="169"/>
+    </row>
+    <row r="82" s="53" customFormat="1" customHeight="1" spans="2:20">
+      <c r="B82" s="140" t="s">
         <v>734</v>
       </c>
-      <c r="B82" s="140"/>
       <c r="C82" s="140"/>
       <c r="D82" s="140"/>
       <c r="E82" s="140"/>
@@ -20558,14 +20635,14 @@
       <c r="L82" s="140"/>
       <c r="M82" s="140"/>
       <c r="N82" s="140"/>
-      <c r="O82" s="176"/>
-      <c r="P82" s="159"/>
-    </row>
-    <row r="83" s="53" customFormat="1" ht="27" customHeight="1" spans="1:19">
-      <c r="A83" s="177" t="s">
+      <c r="O82" s="140"/>
+      <c r="P82" s="176"/>
+      <c r="Q82" s="159"/>
+    </row>
+    <row r="83" s="53" customFormat="1" ht="27" customHeight="1" spans="2:20">
+      <c r="B83" s="177" t="s">
         <v>735</v>
       </c>
-      <c r="B83" s="177"/>
       <c r="C83" s="177"/>
       <c r="D83" s="177"/>
       <c r="E83" s="177"/>
@@ -20578,142 +20655,142 @@
       <c r="L83" s="177"/>
       <c r="M83" s="177"/>
       <c r="N83" s="177"/>
-      <c r="O83" s="159"/>
+      <c r="O83" s="177"/>
       <c r="P83" s="159"/>
-    </row>
-    <row r="84" s="54" customFormat="1" ht="29.25" customHeight="1" spans="1:19">
-      <c r="A84" s="178" t="s">
+      <c r="Q83" s="159"/>
+    </row>
+    <row r="84" s="54" customFormat="1" ht="29.25" customHeight="1" spans="2:20">
+      <c r="B84" s="178" t="s">
         <v>736</v>
       </c>
-      <c r="B84" s="178" t="s">
+      <c r="C84" s="178" t="s">
         <v>156</v>
       </c>
-      <c r="C84" s="178" t="s">
+      <c r="D84" s="178" t="s">
         <v>157</v>
       </c>
-      <c r="D84" s="178" t="s">
+      <c r="E84" s="178" t="s">
         <v>158</v>
       </c>
-      <c r="E84" s="179">
+      <c r="F84" s="179">
         <v>1</v>
       </c>
-      <c r="F84" s="135">
+      <c r="G84" s="135">
         <v>2</v>
       </c>
-      <c r="G84" s="178" t="s">
+      <c r="H84" s="178" t="s">
         <v>159</v>
       </c>
-      <c r="H84" s="179">
+      <c r="I84" s="179">
         <v>1</v>
-      </c>
-      <c r="I84" s="180">
-        <v>4</v>
       </c>
       <c r="J84" s="180">
         <v>4</v>
       </c>
-      <c r="K84" s="179">
+      <c r="K84" s="180">
+        <v>4</v>
+      </c>
+      <c r="L84" s="179">
         <v>1</v>
       </c>
-      <c r="L84" s="179" t="s">
+      <c r="M84" s="179" t="s">
         <v>731</v>
       </c>
-      <c r="M84" s="181">
+      <c r="N84" s="181">
         <v>1</v>
       </c>
-      <c r="N84" s="178" t="s">
+      <c r="O84" s="178" t="s">
         <v>158</v>
       </c>
-      <c r="O84" s="169"/>
       <c r="P84" s="169"/>
-    </row>
-    <row r="85" s="54" customFormat="1" ht="30.75" customHeight="1" spans="1:19">
-      <c r="A85" s="178"/>
+      <c r="Q84" s="169"/>
+    </row>
+    <row r="85" s="54" customFormat="1" ht="30.75" customHeight="1" spans="2:20">
       <c r="B85" s="178"/>
-      <c r="C85" s="178" t="s">
+      <c r="C85" s="178"/>
+      <c r="D85" s="178" t="s">
         <v>160</v>
       </c>
-      <c r="D85" s="178" t="s">
+      <c r="E85" s="178" t="s">
         <v>161</v>
       </c>
-      <c r="E85" s="178" t="s">
+      <c r="F85" s="178" t="s">
         <v>162</v>
       </c>
-      <c r="F85" s="141" t="s">
+      <c r="G85" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="G85" s="178" t="s">
+      <c r="H85" s="178" t="s">
         <v>444</v>
       </c>
-      <c r="H85" s="178" t="s">
+      <c r="I85" s="178" t="s">
         <v>164</v>
       </c>
-      <c r="I85" s="182" t="s">
+      <c r="J85" s="182" t="s">
         <v>26</v>
       </c>
-      <c r="J85" s="182" t="s">
+      <c r="K85" s="182" t="s">
         <v>27</v>
       </c>
-      <c r="K85" s="178" t="s">
+      <c r="L85" s="178" t="s">
         <v>167</v>
       </c>
-      <c r="L85" s="178" t="s">
+      <c r="M85" s="178" t="s">
         <v>737</v>
       </c>
-      <c r="M85" s="178" t="s">
+      <c r="N85" s="178" t="s">
         <v>704</v>
       </c>
-      <c r="N85" s="178" t="s">
+      <c r="O85" s="178" t="s">
         <v>170</v>
       </c>
-      <c r="O85" s="169"/>
       <c r="P85" s="169"/>
-    </row>
-    <row r="86" s="54" customFormat="1" ht="30.75" customHeight="1" spans="1:19">
-      <c r="A86" s="178"/>
+      <c r="Q85" s="169"/>
+    </row>
+    <row r="86" s="54" customFormat="1" ht="30.75" customHeight="1" spans="2:20">
       <c r="B86" s="178"/>
-      <c r="C86" s="178" t="s">
+      <c r="C86" s="178"/>
+      <c r="D86" s="178" t="s">
         <v>705</v>
       </c>
-      <c r="D86" s="178" t="s">
+      <c r="E86" s="178" t="s">
         <v>172</v>
       </c>
-      <c r="E86" s="178" t="s">
+      <c r="F86" s="178" t="s">
         <v>46</v>
       </c>
-      <c r="F86" s="149" t="s">
+      <c r="G86" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="G86" s="178" t="s">
+      <c r="H86" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="H86" s="178" t="s">
+      <c r="I86" s="178" t="s">
         <v>138</v>
-      </c>
-      <c r="I86" s="182" t="s">
-        <v>50</v>
       </c>
       <c r="J86" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="K86" s="178" t="s">
+      <c r="K86" s="182" t="s">
+        <v>50</v>
+      </c>
+      <c r="L86" s="178" t="s">
         <v>731</v>
       </c>
-      <c r="L86" s="178" t="s">
+      <c r="M86" s="178" t="s">
         <v>733</v>
       </c>
-      <c r="M86" s="181"/>
-      <c r="N86" s="178" t="s">
+      <c r="N86" s="181"/>
+      <c r="O86" s="178" t="s">
         <v>54</v>
       </c>
-      <c r="O86" s="169"/>
       <c r="P86" s="169"/>
-    </row>
-    <row r="89" s="53" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A89" s="183" t="s">
+      <c r="Q86" s="169"/>
+    </row>
+    <row r="89" s="53" customFormat="1" customHeight="1" spans="2:20">
+      <c r="B89" s="183" t="s">
         <v>738</v>
       </c>
-      <c r="B89" s="183"/>
       <c r="C89" s="183"/>
       <c r="D89" s="183"/>
       <c r="E89" s="183"/>
@@ -20726,182 +20803,182 @@
       <c r="L89" s="183"/>
       <c r="M89" s="183"/>
       <c r="N89" s="183"/>
-      <c r="O89" s="184"/>
-      <c r="P89" s="185"/>
-      <c r="Q89" s="186"/>
-      <c r="R89" s="187"/>
-      <c r="S89" s="188"/>
-    </row>
-    <row r="90" s="53" customFormat="1" ht="32.25" customHeight="1" spans="1:19">
-      <c r="A90" s="121" t="s">
+      <c r="O89" s="183"/>
+      <c r="P89" s="184"/>
+      <c r="Q89" s="185"/>
+      <c r="R89" s="186"/>
+      <c r="S89" s="187"/>
+      <c r="T89" s="188"/>
+    </row>
+    <row r="90" s="53" customFormat="1" ht="32.25" customHeight="1" spans="2:20">
+      <c r="B90" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="189" t="s">
+      <c r="C90" s="189" t="s">
         <v>678</v>
       </c>
-      <c r="C90" s="190" t="s">
+      <c r="D90" s="190" t="s">
         <v>157</v>
       </c>
-      <c r="D90" s="190" t="s">
+      <c r="E90" s="190" t="s">
         <v>158</v>
       </c>
-      <c r="E90" s="191">
+      <c r="F90" s="191">
         <v>1</v>
       </c>
-      <c r="F90" s="27">
+      <c r="G90" s="27">
         <v>2</v>
       </c>
-      <c r="G90" s="190" t="s">
+      <c r="H90" s="190" t="s">
         <v>159</v>
       </c>
-      <c r="H90" s="192">
+      <c r="I90" s="192">
         <v>1</v>
-      </c>
-      <c r="I90" s="193">
-        <v>4</v>
       </c>
       <c r="J90" s="193">
         <v>4</v>
       </c>
-      <c r="K90" s="192">
+      <c r="K90" s="193">
+        <v>4</v>
+      </c>
+      <c r="L90" s="192">
         <v>1</v>
-      </c>
-      <c r="L90" s="194" t="s">
-        <v>412</v>
       </c>
       <c r="M90" s="194" t="s">
         <v>412</v>
       </c>
-      <c r="N90" s="192">
+      <c r="N90" s="194" t="s">
+        <v>412</v>
+      </c>
+      <c r="O90" s="192">
         <v>1</v>
       </c>
-      <c r="O90" s="195">
+      <c r="P90" s="195">
         <v>1</v>
       </c>
-      <c r="P90" s="196">
+      <c r="Q90" s="196">
         <v>1</v>
       </c>
-      <c r="Q90" s="197">
+      <c r="R90" s="197">
         <v>1</v>
       </c>
-      <c r="R90" s="26">
+      <c r="S90" s="26">
         <v>1</v>
       </c>
-      <c r="S90" s="25">
+      <c r="T90" s="25">
         <v>1</v>
       </c>
     </row>
-    <row r="91" s="53" customFormat="1" ht="27.75" customHeight="1" spans="1:19">
-      <c r="A91" s="198"/>
-      <c r="B91" s="189"/>
-      <c r="C91" s="190" t="s">
+    <row r="91" s="53" customFormat="1" ht="27.75" customHeight="1" spans="2:20">
+      <c r="B91" s="198"/>
+      <c r="C91" s="189"/>
+      <c r="D91" s="190" t="s">
         <v>160</v>
       </c>
-      <c r="D91" s="190" t="s">
+      <c r="E91" s="190" t="s">
         <v>161</v>
       </c>
-      <c r="E91" s="190" t="s">
+      <c r="F91" s="190" t="s">
         <v>162</v>
       </c>
-      <c r="F91" s="31" t="s">
+      <c r="G91" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="G91" s="190" t="s">
+      <c r="H91" s="190" t="s">
         <v>444</v>
       </c>
-      <c r="H91" s="194" t="s">
+      <c r="I91" s="194" t="s">
         <v>164</v>
       </c>
-      <c r="I91" s="189" t="s">
+      <c r="J91" s="189" t="s">
         <v>26</v>
       </c>
-      <c r="J91" s="189" t="s">
+      <c r="K91" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="K91" s="194" t="s">
+      <c r="L91" s="194" t="s">
         <v>167</v>
       </c>
-      <c r="L91" s="121" t="s">
+      <c r="M91" s="121" t="s">
         <v>739</v>
       </c>
-      <c r="M91" s="199" t="s">
+      <c r="N91" s="199" t="s">
         <v>740</v>
       </c>
-      <c r="N91" s="121" t="s">
+      <c r="O91" s="121" t="s">
         <v>741</v>
       </c>
-      <c r="O91" s="200" t="s">
+      <c r="P91" s="200" t="s">
         <v>742</v>
       </c>
-      <c r="P91" s="201" t="s">
+      <c r="Q91" s="201" t="s">
         <v>743</v>
       </c>
-      <c r="Q91" s="202" t="s">
+      <c r="R91" s="202" t="s">
         <v>744</v>
       </c>
-      <c r="R91" s="203" t="s">
+      <c r="S91" s="203" t="s">
         <v>745</v>
       </c>
-      <c r="S91" s="204" t="s">
+      <c r="T91" s="204" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="92" s="53" customFormat="1" ht="24.75" customHeight="1" spans="1:19">
-      <c r="A92" s="198"/>
-      <c r="B92" s="189"/>
-      <c r="C92" s="190" t="s">
+    <row r="92" s="53" customFormat="1" ht="24.75" customHeight="1" spans="2:20">
+      <c r="B92" s="198"/>
+      <c r="C92" s="189"/>
+      <c r="D92" s="190" t="s">
         <v>705</v>
       </c>
-      <c r="D92" s="205" t="s">
+      <c r="E92" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="E92" s="31" t="s">
+      <c r="F92" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="F92" s="35" t="s">
+      <c r="G92" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="G92" s="190" t="s">
+      <c r="H92" s="190" t="s">
         <v>48</v>
       </c>
-      <c r="H92" s="206" t="s">
+      <c r="I92" s="206" t="s">
         <v>140</v>
-      </c>
-      <c r="I92" s="194" t="s">
-        <v>50</v>
       </c>
       <c r="J92" s="194" t="s">
         <v>50</v>
       </c>
-      <c r="K92" s="206" t="s">
+      <c r="K92" s="194" t="s">
+        <v>50</v>
+      </c>
+      <c r="L92" s="206" t="s">
         <v>746</v>
       </c>
-      <c r="L92" s="194" t="s">
+      <c r="M92" s="194" t="s">
         <v>747</v>
       </c>
-      <c r="M92" s="194" t="s">
+      <c r="N92" s="194" t="s">
         <v>748</v>
       </c>
-      <c r="N92" s="207" t="s">
+      <c r="O92" s="207" t="s">
         <v>749</v>
       </c>
-      <c r="O92" s="208" t="s">
+      <c r="P92" s="208" t="s">
         <v>747</v>
       </c>
-      <c r="P92" s="36" t="s">
+      <c r="Q92" s="36" t="s">
         <v>749</v>
       </c>
-      <c r="Q92" s="209" t="s">
+      <c r="R92" s="209" t="s">
         <v>750</v>
       </c>
-      <c r="R92" s="210" t="s">
+      <c r="S92" s="210" t="s">
         <v>747</v>
       </c>
-      <c r="S92" s="188"/>
-    </row>
-    <row r="93" s="53" customFormat="1" ht="192.75" customHeight="1" spans="1:19">
-      <c r="A93" s="211"/>
-      <c r="B93" s="212"/>
+      <c r="T92" s="188"/>
+    </row>
+    <row r="93" s="53" customFormat="1" ht="192.75" customHeight="1" spans="2:20">
+      <c r="B93" s="211"/>
       <c r="C93" s="212"/>
       <c r="D93" s="212"/>
       <c r="E93" s="212"/>
@@ -20911,31 +20988,31 @@
       <c r="I93" s="212"/>
       <c r="J93" s="212"/>
       <c r="K93" s="212"/>
-      <c r="L93" s="212" t="s">
+      <c r="L93" s="212"/>
+      <c r="M93" s="212" t="s">
         <v>751</v>
       </c>
-      <c r="M93" s="213" t="s">
+      <c r="N93" s="213" t="s">
         <v>752</v>
       </c>
-      <c r="N93" s="214" t="s">
+      <c r="O93" s="214" t="s">
         <v>753</v>
       </c>
-      <c r="O93" s="215" t="s">
+      <c r="P93" s="215" t="s">
         <v>754</v>
       </c>
-      <c r="P93" s="214" t="s">
+      <c r="Q93" s="214" t="s">
         <v>755</v>
       </c>
-      <c r="Q93" s="216" t="s">
+      <c r="R93" s="216" t="s">
         <v>756</v>
       </c>
-      <c r="R93" s="214" t="s">
+      <c r="S93" s="214" t="s">
         <v>757</v>
       </c>
-      <c r="S93" s="188"/>
-    </row>
-    <row r="94" s="53" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A94" s="217"/>
+      <c r="T93" s="188"/>
+    </row>
+    <row r="94" s="53" customFormat="1" customHeight="1" spans="2:20">
       <c r="B94" s="217"/>
       <c r="C94" s="217"/>
       <c r="D94" s="217"/>
@@ -20954,9 +21031,9 @@
       <c r="Q94" s="217"/>
       <c r="R94" s="217"/>
       <c r="S94" s="217"/>
-    </row>
-    <row r="95" s="53" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A95" s="217"/>
+      <c r="T94" s="217"/>
+    </row>
+    <row r="95" s="53" customFormat="1" customHeight="1" spans="2:20">
       <c r="B95" s="217"/>
       <c r="C95" s="217"/>
       <c r="D95" s="217"/>
@@ -20975,12 +21052,12 @@
       <c r="Q95" s="217"/>
       <c r="R95" s="217"/>
       <c r="S95" s="217"/>
-    </row>
-    <row r="96" s="53" customFormat="1" ht="46.5" customHeight="1" spans="1:19">
-      <c r="A96" s="183" t="s">
+      <c r="T95" s="217"/>
+    </row>
+    <row r="96" s="53" customFormat="1" ht="46.5" customHeight="1" spans="2:20">
+      <c r="B96" s="183" t="s">
         <v>758</v>
       </c>
-      <c r="B96" s="183"/>
       <c r="C96" s="183"/>
       <c r="D96" s="183"/>
       <c r="E96" s="183"/>
@@ -20994,204 +21071,204 @@
       <c r="M96" s="183"/>
       <c r="N96" s="183"/>
       <c r="O96" s="183"/>
-      <c r="P96" s="218"/>
-      <c r="Q96" s="219"/>
-      <c r="R96" s="187"/>
-      <c r="S96" s="188"/>
-    </row>
-    <row r="97" s="53" customFormat="1" ht="32.25" customHeight="1" spans="1:19">
-      <c r="A97" s="121" t="s">
+      <c r="P96" s="183"/>
+      <c r="Q96" s="218"/>
+      <c r="R96" s="219"/>
+      <c r="S96" s="187"/>
+      <c r="T96" s="188"/>
+    </row>
+    <row r="97" s="53" customFormat="1" ht="32.25" customHeight="1" spans="2:20">
+      <c r="B97" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="B97" s="189" t="s">
+      <c r="C97" s="189" t="s">
         <v>678</v>
       </c>
-      <c r="C97" s="190" t="s">
+      <c r="D97" s="190" t="s">
         <v>157</v>
       </c>
-      <c r="D97" s="190" t="s">
+      <c r="E97" s="190" t="s">
         <v>158</v>
       </c>
-      <c r="E97" s="191">
+      <c r="F97" s="191">
         <v>1</v>
       </c>
-      <c r="F97" s="27">
+      <c r="G97" s="27">
         <v>2</v>
       </c>
-      <c r="G97" s="190" t="s">
+      <c r="H97" s="190" t="s">
         <v>159</v>
       </c>
-      <c r="H97" s="192">
+      <c r="I97" s="192">
         <v>1</v>
-      </c>
-      <c r="I97" s="193">
-        <v>4</v>
       </c>
       <c r="J97" s="193">
         <v>4</v>
       </c>
-      <c r="K97" s="192">
+      <c r="K97" s="193">
+        <v>4</v>
+      </c>
+      <c r="L97" s="192">
         <v>1</v>
-      </c>
-      <c r="L97" s="194" t="s">
-        <v>412</v>
       </c>
       <c r="M97" s="194" t="s">
         <v>412</v>
       </c>
-      <c r="N97" s="192">
+      <c r="N97" s="194" t="s">
+        <v>412</v>
+      </c>
+      <c r="O97" s="192">
         <v>1</v>
       </c>
-      <c r="O97" s="195">
+      <c r="P97" s="195">
         <v>1</v>
       </c>
-      <c r="P97" s="196">
-        <v>1</v>
-      </c>
-      <c r="Q97" s="26">
+      <c r="Q97" s="196">
         <v>1</v>
       </c>
       <c r="R97" s="26">
         <v>1</v>
       </c>
-      <c r="S97" s="25">
+      <c r="S97" s="26">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" s="53" customFormat="1" ht="27.75" customHeight="1" spans="1:19">
-      <c r="A98" s="198"/>
-      <c r="B98" s="189"/>
-      <c r="C98" s="190" t="s">
+      <c r="T97" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" s="53" customFormat="1" ht="27.75" customHeight="1" spans="2:20">
+      <c r="B98" s="198"/>
+      <c r="C98" s="189"/>
+      <c r="D98" s="190" t="s">
         <v>160</v>
       </c>
-      <c r="D98" s="190" t="s">
+      <c r="E98" s="190" t="s">
         <v>161</v>
       </c>
-      <c r="E98" s="190" t="s">
+      <c r="F98" s="190" t="s">
         <v>162</v>
       </c>
-      <c r="F98" s="31" t="s">
+      <c r="G98" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="G98" s="190" t="s">
+      <c r="H98" s="190" t="s">
         <v>444</v>
       </c>
-      <c r="H98" s="194" t="s">
+      <c r="I98" s="194" t="s">
         <v>164</v>
       </c>
-      <c r="I98" s="189" t="s">
+      <c r="J98" s="189" t="s">
         <v>26</v>
       </c>
-      <c r="J98" s="189" t="s">
+      <c r="K98" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="K98" s="194" t="s">
+      <c r="L98" s="194" t="s">
         <v>167</v>
       </c>
-      <c r="L98" s="121" t="s">
+      <c r="M98" s="121" t="s">
         <v>739</v>
       </c>
-      <c r="M98" s="199" t="s">
+      <c r="N98" s="199" t="s">
         <v>759</v>
       </c>
-      <c r="N98" s="121" t="s">
+      <c r="O98" s="121" t="s">
         <v>741</v>
       </c>
-      <c r="O98" s="200" t="s">
+      <c r="P98" s="200" t="s">
         <v>742</v>
       </c>
-      <c r="P98" s="201" t="s">
+      <c r="Q98" s="201" t="s">
         <v>743</v>
       </c>
-      <c r="Q98" s="203" t="s">
+      <c r="R98" s="203" t="s">
         <v>744</v>
       </c>
-      <c r="R98" s="203" t="s">
+      <c r="S98" s="203" t="s">
         <v>745</v>
       </c>
-      <c r="S98" s="204" t="s">
+      <c r="T98" s="204" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="99" s="53" customFormat="1" ht="24.75" customHeight="1" spans="1:19">
-      <c r="A99" s="198"/>
-      <c r="B99" s="189"/>
-      <c r="C99" s="190" t="s">
+    <row r="99" s="53" customFormat="1" ht="24.75" customHeight="1" spans="2:20">
+      <c r="B99" s="198"/>
+      <c r="C99" s="189"/>
+      <c r="D99" s="190" t="s">
         <v>705</v>
       </c>
-      <c r="D99" s="205" t="s">
+      <c r="E99" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="E99" s="31" t="s">
+      <c r="F99" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="F99" s="35" t="s">
+      <c r="G99" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="G99" s="190" t="s">
+      <c r="H99" s="190" t="s">
         <v>48</v>
       </c>
-      <c r="H99" s="206" t="s">
+      <c r="I99" s="206" t="s">
         <v>142</v>
-      </c>
-      <c r="I99" s="194" t="s">
-        <v>50</v>
       </c>
       <c r="J99" s="194" t="s">
         <v>50</v>
       </c>
-      <c r="K99" s="206" t="s">
+      <c r="K99" s="194" t="s">
+        <v>50</v>
+      </c>
+      <c r="L99" s="206" t="s">
         <v>664</v>
       </c>
-      <c r="L99" s="194" t="s">
+      <c r="M99" s="194" t="s">
         <v>747</v>
       </c>
-      <c r="M99" s="220" t="s">
+      <c r="N99" s="220" t="s">
         <v>760</v>
       </c>
-      <c r="N99" s="207" t="s">
+      <c r="O99" s="207" t="s">
         <v>749</v>
       </c>
-      <c r="O99" s="207" t="s">
+      <c r="P99" s="207" t="s">
         <v>747</v>
       </c>
-      <c r="P99" s="36" t="s">
+      <c r="Q99" s="36" t="s">
         <v>749</v>
       </c>
-      <c r="Q99" s="209" t="s">
+      <c r="R99" s="209" t="s">
         <v>750</v>
       </c>
-      <c r="R99" s="210" t="s">
+      <c r="S99" s="210" t="s">
         <v>747</v>
       </c>
-      <c r="S99" s="188"/>
-    </row>
-    <row r="100" s="53" customFormat="1" ht="40.5" customHeight="1" spans="1:19">
-      <c r="A100" s="198"/>
-      <c r="B100" s="189"/>
-      <c r="C100" s="190"/>
-      <c r="D100" s="205"/>
-      <c r="E100" s="221"/>
+      <c r="T99" s="188"/>
+    </row>
+    <row r="100" s="53" customFormat="1" ht="40.5" customHeight="1" spans="2:20">
+      <c r="B100" s="198"/>
+      <c r="C100" s="189"/>
+      <c r="D100" s="190"/>
+      <c r="E100" s="205"/>
       <c r="F100" s="221"/>
-      <c r="G100" s="190"/>
-      <c r="H100" s="206"/>
-      <c r="I100" s="194"/>
+      <c r="G100" s="221"/>
+      <c r="H100" s="190"/>
+      <c r="I100" s="206"/>
       <c r="J100" s="194"/>
-      <c r="K100" s="206"/>
-      <c r="L100" s="222"/>
-      <c r="M100" s="223"/>
-      <c r="N100" s="224" t="s">
+      <c r="K100" s="194"/>
+      <c r="L100" s="206"/>
+      <c r="M100" s="222"/>
+      <c r="N100" s="223"/>
+      <c r="O100" s="224" t="s">
         <v>761</v>
       </c>
-      <c r="O100" s="225"/>
       <c r="P100" s="225"/>
       <c r="Q100" s="225"/>
-      <c r="R100" s="226"/>
-      <c r="S100" s="188"/>
-    </row>
-    <row r="101" s="53" customFormat="1" ht="213" customHeight="1" spans="1:19">
-      <c r="A101" s="211"/>
-      <c r="B101" s="212"/>
+      <c r="R100" s="225"/>
+      <c r="S100" s="226"/>
+      <c r="T100" s="188"/>
+    </row>
+    <row r="101" s="53" customFormat="1" ht="213" customHeight="1" spans="2:20">
+      <c r="B101" s="211"/>
       <c r="C101" s="212"/>
       <c r="D101" s="212"/>
       <c r="E101" s="212"/>
@@ -21201,88 +21278,72 @@
       <c r="I101" s="212"/>
       <c r="J101" s="212"/>
       <c r="K101" s="212"/>
-      <c r="L101" s="212" t="s">
+      <c r="L101" s="212"/>
+      <c r="M101" s="212" t="s">
         <v>751</v>
       </c>
-      <c r="M101" s="227" t="s">
+      <c r="N101" s="227" t="s">
         <v>762</v>
       </c>
-      <c r="N101" s="228" t="s">
+      <c r="O101" s="228" t="s">
         <v>753</v>
       </c>
-      <c r="O101" s="228" t="s">
+      <c r="P101" s="228" t="s">
         <v>754</v>
       </c>
-      <c r="P101" s="214" t="s">
+      <c r="Q101" s="214" t="s">
         <v>755</v>
       </c>
-      <c r="Q101" s="216" t="s">
+      <c r="R101" s="216" t="s">
         <v>756</v>
       </c>
-      <c r="R101" s="228" t="s">
+      <c r="S101" s="228" t="s">
         <v>757</v>
       </c>
-      <c r="S101" s="188"/>
+      <c r="T101" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A10:P10"/>
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="A16:P16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A20:P20"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A35:P35"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="A41:O41"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A47:O47"/>
-    <mergeCell ref="A51:O51"/>
-    <mergeCell ref="A53:O53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="A65:P65"/>
-    <mergeCell ref="A71:P71"/>
-    <mergeCell ref="A75:P75"/>
-    <mergeCell ref="A78:N78"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A83:N83"/>
-    <mergeCell ref="A89:O89"/>
-    <mergeCell ref="A96:O96"/>
-    <mergeCell ref="N100:R100"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="A84:A86"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="A97:A99"/>
+    <mergeCell ref="B1:Q1"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="B6:Q6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="B10:Q10"/>
+    <mergeCell ref="B11:Q11"/>
+    <mergeCell ref="B16:Q16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="B20:Q20"/>
+    <mergeCell ref="B23:P23"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B32:P32"/>
+    <mergeCell ref="B35:Q35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="B41:P41"/>
+    <mergeCell ref="B45:P45"/>
+    <mergeCell ref="B47:P47"/>
+    <mergeCell ref="B51:P51"/>
+    <mergeCell ref="B53:P53"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="B71:Q71"/>
+    <mergeCell ref="B75:Q75"/>
+    <mergeCell ref="B78:O78"/>
+    <mergeCell ref="B82:O82"/>
+    <mergeCell ref="B83:O83"/>
+    <mergeCell ref="B89:P89"/>
+    <mergeCell ref="B96:P96"/>
+    <mergeCell ref="O100:S100"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B12:B14"/>
@@ -21300,6 +21361,23 @@
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="B90:B92"/>
     <mergeCell ref="B97:B99"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="C97:C99"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277777777777778" footer="0.277777777777778"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -21587,7 +21665,7 @@
         <v>767</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>46</v>
@@ -21943,7 +22021,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="B2:G58"/>
+  <dimension ref="B2:G74"/>
   <sheetFormatPr defaultColWidth="10.5714285714286" defaultRowHeight="12.75" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.5714285714286" style="4"/>
@@ -22285,240 +22363,379 @@
     </row>
     <row r="35" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="14"/>
+      <c r="C35" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>837</v>
+      </c>
       <c r="E35" s="9"/>
     </row>
     <row r="36" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>839</v>
+      </c>
       <c r="E36" s="9"/>
     </row>
     <row r="37" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B37" s="8"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="9"/>
-    </row>
-    <row r="38" s="4" customFormat="1" ht="19.5" customHeight="1" spans="2:5">
-      <c r="B38" s="8" t="s">
-        <v>836</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="13"/>
-    </row>
-    <row r="39" s="4" customFormat="1" ht="20.25" customHeight="1" spans="2:5">
+      <c r="C37" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>841</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B38" s="8"/>
+      <c r="C38" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>844</v>
+      </c>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B39" s="8"/>
       <c r="C39" s="9" t="s">
-        <v>837</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>838</v>
+        <v>845</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>846</v>
       </c>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" s="4" customFormat="1" ht="19.5" customHeight="1" spans="2:5">
+    <row r="40" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B40" s="8"/>
       <c r="C40" s="9" t="s">
-        <v>839</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>840</v>
+        <v>847</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>848</v>
       </c>
       <c r="E40" s="9"/>
     </row>
     <row r="41" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B41" s="8"/>
       <c r="C41" s="9" t="s">
-        <v>841</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>842</v>
+        <v>849</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>850</v>
       </c>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" s="4" customFormat="1" ht="21.75" customHeight="1" spans="2:5">
+    <row r="42" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B42" s="8"/>
       <c r="C42" s="9" t="s">
-        <v>843</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>844</v>
+        <v>851</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>852</v>
       </c>
       <c r="E42" s="9"/>
     </row>
     <row r="43" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B43" s="8"/>
       <c r="C43" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>846</v>
+        <v>853</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>854</v>
       </c>
       <c r="E43" s="9"/>
     </row>
     <row r="44" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B44" s="8"/>
       <c r="C44" s="9" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>848</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>849</v>
-      </c>
+        <v>856</v>
+      </c>
+      <c r="E44" s="9"/>
     </row>
     <row r="45" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B45" s="8"/>
-      <c r="C45" s="9" t="s">
-        <v>850</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>851</v>
-      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="14"/>
       <c r="E45" s="9"/>
     </row>
     <row r="46" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B46" s="8"/>
-      <c r="C46" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>853</v>
-      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="14"/>
       <c r="E46" s="9"/>
     </row>
     <row r="47" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B47" s="8"/>
-      <c r="C47" s="9" t="s">
-        <v>854</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>855</v>
-      </c>
+      <c r="C47" s="9"/>
+      <c r="D47" s="14"/>
       <c r="E47" s="9"/>
     </row>
-    <row r="48" s="4" customFormat="1" ht="23.25" customHeight="1" spans="2:5">
+    <row r="48" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B48" s="8"/>
-      <c r="C48" s="9" t="s">
-        <v>856</v>
-      </c>
-      <c r="D48" s="9" t="s">
+      <c r="C48" s="9"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="9"/>
+    </row>
+    <row r="49" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B49" s="8"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="9"/>
+    </row>
+    <row r="50" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B50" s="8"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="9"/>
+    </row>
+    <row r="51" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B51" s="8"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B52" s="8"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="9"/>
+    </row>
+    <row r="53" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B53" s="8"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="9"/>
+    </row>
+    <row r="54" s="4" customFormat="1" ht="19.5" customHeight="1" spans="2:5">
+      <c r="B54" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="E48" s="17"/>
-    </row>
-    <row r="49" s="4" customFormat="1" ht="22.5" customHeight="1" spans="2:5">
-      <c r="B49" s="8"/>
-      <c r="C49" s="9" t="s">
-        <v>858</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>859</v>
-      </c>
-      <c r="E49" s="9"/>
-    </row>
-    <row r="50" s="4" customFormat="1" ht="21" customHeight="1" spans="2:5">
-      <c r="B50" s="16"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-    </row>
-    <row r="51" s="4" customFormat="1" ht="21" customHeight="1" spans="2:5">
-      <c r="B51" s="16"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-    </row>
-    <row r="52" s="4" customFormat="1" ht="20.1" customHeight="1" spans="2:5">
-      <c r="B52" s="8" t="s">
-        <v>860</v>
-      </c>
-      <c r="C52" s="9">
-        <v>0</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>780</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="53" s="4" customFormat="1" ht="27" customHeight="1" spans="2:5">
-      <c r="B53" s="8"/>
-      <c r="C53" s="9" t="s">
-        <v>862</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>863</v>
-      </c>
-      <c r="E53" s="13"/>
-    </row>
-    <row r="54" s="4" customFormat="1" ht="35.25" customHeight="1" spans="2:5">
-      <c r="B54" s="8"/>
-      <c r="C54" s="9" t="s">
-        <v>864</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>865</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="55" s="4" customFormat="1" ht="33.75" customHeight="1" spans="2:5">
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="13"/>
+    </row>
+    <row r="55" s="4" customFormat="1" ht="20.25" customHeight="1" spans="2:5">
       <c r="B55" s="8"/>
       <c r="C55" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>868</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="56" s="4" customFormat="1" ht="36.75" customHeight="1" spans="2:5">
+        <v>858</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="E55" s="9"/>
+    </row>
+    <row r="56" s="4" customFormat="1" ht="19.5" customHeight="1" spans="2:5">
       <c r="B56" s="8"/>
       <c r="C56" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>871</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="57" s="4" customFormat="1" ht="35.25" customHeight="1" spans="2:5">
+        <v>860</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="E56" s="9"/>
+    </row>
+    <row r="57" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
       <c r="B57" s="8"/>
       <c r="C57" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="E57" s="9"/>
+    </row>
+    <row r="58" s="4" customFormat="1" ht="21.75" customHeight="1" spans="2:5">
+      <c r="B58" s="8"/>
+      <c r="C58" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="E58" s="9"/>
+    </row>
+    <row r="59" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B59" s="8"/>
+      <c r="C59" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B60" s="8"/>
+      <c r="C60" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>869</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="61" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B61" s="8"/>
+      <c r="C61" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>872</v>
+      </c>
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B62" s="8"/>
+      <c r="C62" s="9" t="s">
         <v>873</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D62" s="14" t="s">
         <v>874</v>
       </c>
-      <c r="E57" s="18" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="58" s="4" customFormat="1" ht="21" customHeight="1" spans="2:5">
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
+      <c r="E62" s="9"/>
+    </row>
+    <row r="63" s="4" customFormat="1" ht="24" customHeight="1" spans="2:5">
+      <c r="B63" s="8"/>
+      <c r="C63" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>876</v>
+      </c>
+      <c r="E63" s="9"/>
+    </row>
+    <row r="64" s="4" customFormat="1" ht="23.25" customHeight="1" spans="2:5">
+      <c r="B64" s="8"/>
+      <c r="C64" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="E64" s="17"/>
+    </row>
+    <row r="65" s="4" customFormat="1" ht="22.5" customHeight="1" spans="2:5">
+      <c r="B65" s="8"/>
+      <c r="C65" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>880</v>
+      </c>
+      <c r="E65" s="9"/>
+    </row>
+    <row r="66" s="4" customFormat="1" ht="21" customHeight="1" spans="2:5">
+      <c r="B66" s="16"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+    </row>
+    <row r="67" s="4" customFormat="1" ht="21" customHeight="1" spans="2:5">
+      <c r="B67" s="16"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+    </row>
+    <row r="68" s="4" customFormat="1" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B68" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="C68" s="9">
+        <v>0</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="69" s="4" customFormat="1" ht="27" customHeight="1" spans="2:5">
+      <c r="B69" s="8"/>
+      <c r="C69" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>884</v>
+      </c>
+      <c r="E69" s="13"/>
+    </row>
+    <row r="70" s="4" customFormat="1" ht="35.25" customHeight="1" spans="2:5">
+      <c r="B70" s="8"/>
+      <c r="C70" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>886</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="71" s="4" customFormat="1" ht="33.75" customHeight="1" spans="2:5">
+      <c r="B71" s="8"/>
+      <c r="C71" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>889</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="72" s="4" customFormat="1" ht="36.75" customHeight="1" spans="2:5">
+      <c r="B72" s="8"/>
+      <c r="C72" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>892</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="73" s="4" customFormat="1" ht="35.25" customHeight="1" spans="2:5">
+      <c r="B73" s="8"/>
+      <c r="C73" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>895</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="74" s="4" customFormat="1" ht="21" customHeight="1" spans="2:5">
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B5:B15"/>
-    <mergeCell ref="B17:B35"/>
-    <mergeCell ref="B38:B49"/>
-    <mergeCell ref="B52:B57"/>
+    <mergeCell ref="B17:B51"/>
+    <mergeCell ref="B54:B65"/>
+    <mergeCell ref="B68:B73"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="E29:E34"/>
-    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="E37:E42"/>
+    <mergeCell ref="E60:E63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="260" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
@@ -22543,13 +22760,13 @@
   <sheetData>
     <row r="2" s="4" customFormat="1" ht="29.25" customHeight="1" spans="2:5">
       <c r="B2" s="5" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>211</v>
@@ -22562,90 +22779,90 @@
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="10" t="s">
-        <v>877</v>
+        <v>898</v>
       </c>
     </row>
     <row r="4" s="4" customFormat="1" ht="63" customHeight="1" spans="2:5">
       <c r="B4" s="11" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="E4" s="12"/>
     </row>
     <row r="5" s="4" customFormat="1" ht="63" customHeight="1" spans="2:5">
       <c r="B5" s="11" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>882</v>
+        <v>903</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="E5" s="12"/>
     </row>
     <row r="6" s="4" customFormat="1" ht="63" customHeight="1" spans="2:5">
       <c r="B6" s="11" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="E6" s="13"/>
     </row>
     <row r="7" s="4" customFormat="1" ht="63" customHeight="1" spans="2:5">
       <c r="B7" s="11" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="E7" s="13"/>
     </row>
     <row r="8" s="4" customFormat="1" ht="63" customHeight="1" spans="2:5">
       <c r="B8" s="11" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="E8" s="9"/>
     </row>
     <row r="9" s="4" customFormat="1" ht="63" customHeight="1" spans="2:5">
       <c r="B9" s="11" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="E9" s="9"/>
     </row>
     <row r="10" s="4" customFormat="1" ht="63" customHeight="1" spans="2:5">
       <c r="B10" s="11" t="s">
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="E10" s="9"/>
     </row>
@@ -22672,7 +22889,7 @@
     </row>
     <row r="2" customFormat="1" ht="18" spans="2:2">
       <c r="B2" s="2" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="2:2">
@@ -22680,7 +22897,7 @@
     </row>
     <row r="4" customFormat="1" ht="18" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="2:2">
@@ -22688,7 +22905,7 @@
     </row>
     <row r="6" customFormat="1" ht="18" spans="2:2">
       <c r="B6" s="2" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="2:2">
@@ -22696,7 +22913,7 @@
     </row>
     <row r="8" customFormat="1" ht="18" spans="2:2">
       <c r="B8" s="2" t="s">
-        <v>896</v>
+        <v>917</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="2:2">
@@ -22704,7 +22921,7 @@
     </row>
     <row r="10" customFormat="1" ht="18" spans="2:2">
       <c r="B10" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
     </row>
   </sheetData>
